--- a/api/xlsx/fr/ReportingOrganisation.xlsx
+++ b/api/xlsx/fr/ReportingOrganisation.xlsx
@@ -22,78 +22,78 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:organisation-type-code</t>
+  </si>
+  <si>
+    <t>codeforiati:hq-country-or-region</t>
+  </si>
+  <si>
     <t>codeforiati:organisation-type</t>
   </si>
   <si>
-    <t>codeforiati:hq-country-or-region</t>
-  </si>
-  <si>
-    <t>codeforiati:organisation-type-code</t>
-  </si>
-  <si>
     <t>AU-5</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
     <t>Government</t>
   </si>
   <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>44000</t>
   </si>
   <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>(No country assigned)</t>
+  </si>
+  <si>
     <t>Multilateral</t>
   </si>
   <si>
-    <t>(No country assigned)</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>US-EIN-941655673</t>
   </si>
   <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
     <t>Foundation</t>
   </si>
   <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>41AAA</t>
   </si>
   <si>
     <t>GB-CHC-1038860</t>
   </si>
   <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
     <t>International NGO</t>
   </si>
   <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>XI-IATI-EC_DEVCO</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>Other Public Sector</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>SE-0</t>
   </si>
   <si>
@@ -163,12 +163,12 @@
     <t>47122</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>Public Private Partnership</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>US-EIN-300108263</t>
   </si>
   <si>
@@ -190,15 +190,15 @@
     <t>NP-CRO-45995/063/064</t>
   </si>
   <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>Nepal</t>
+  </si>
+  <si>
     <t>Academic, Training and Research</t>
   </si>
   <si>
-    <t>Nepal</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
     <t>GB-CHC-327421</t>
   </si>
   <si>
@@ -253,12 +253,12 @@
     <t>GB-CHC-1090745</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>National NGO</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>GB-CHC-298316</t>
   </si>
   <si>
@@ -370,15 +370,15 @@
     <t>ZA-NPO-061-870</t>
   </si>
   <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
     <t>Regional NGO</t>
   </si>
   <si>
-    <t>South Africa</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
     <t>30001</t>
   </si>
   <si>
@@ -472,10 +472,10 @@
     <t>GB-COH-03788027</t>
   </si>
   <si>
+    <t>70</t>
+  </si>
+  <si>
     <t>Private Sector</t>
-  </si>
-  <si>
-    <t>70</t>
   </si>
   <si>
     <t>GB-CHC-1058991</t>

--- a/api/xlsx/fr/ReportingOrganisation.xlsx
+++ b/api/xlsx/fr/ReportingOrganisation.xlsx
@@ -22,12 +22,12 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:organisation-type</t>
+  </si>
+  <si>
     <t>codeforiati:organisation-type-code</t>
   </si>
   <si>
-    <t>codeforiati:organisation-type</t>
-  </si>
-  <si>
     <t>codeforiati:hq-country-or-region</t>
   </si>
   <si>
@@ -37,36 +37,36 @@
     <t>active</t>
   </si>
   <si>
+    <t>Government</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
-    <t>Government</t>
-  </si>
-  <si>
     <t>Australia</t>
   </si>
   <si>
     <t>44000</t>
   </si>
   <si>
+    <t>Multilateral</t>
+  </si>
+  <si>
     <t>40</t>
   </si>
   <si>
-    <t>Multilateral</t>
-  </si>
-  <si>
     <t>(No country assigned)</t>
   </si>
   <si>
     <t>US-EIN-941655673</t>
   </si>
   <si>
+    <t>Foundation</t>
+  </si>
+  <si>
     <t>60</t>
   </si>
   <si>
-    <t>Foundation</t>
-  </si>
-  <si>
     <t>United States</t>
   </si>
   <si>
@@ -76,24 +76,24 @@
     <t>GB-CHC-1038860</t>
   </si>
   <si>
+    <t>International NGO</t>
+  </si>
+  <si>
     <t>21</t>
   </si>
   <si>
-    <t>International NGO</t>
-  </si>
-  <si>
     <t>United Kingdom</t>
   </si>
   <si>
     <t>XI-IATI-EC_DEVCO</t>
   </si>
   <si>
+    <t>Other Public Sector</t>
+  </si>
+  <si>
     <t>15</t>
   </si>
   <si>
-    <t>Other Public Sector</t>
-  </si>
-  <si>
     <t>SE-0</t>
   </si>
   <si>
@@ -163,12 +163,12 @@
     <t>47122</t>
   </si>
   <si>
+    <t>Public Private Partnership</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
-    <t>Public Private Partnership</t>
-  </si>
-  <si>
     <t>US-EIN-300108263</t>
   </si>
   <si>
@@ -190,12 +190,12 @@
     <t>NP-CRO-45995/063/064</t>
   </si>
   <si>
+    <t>Academic, Training and Research</t>
+  </si>
+  <si>
     <t>80</t>
   </si>
   <si>
-    <t>Academic, Training and Research</t>
-  </si>
-  <si>
     <t>Nepal</t>
   </si>
   <si>
@@ -253,12 +253,12 @@
     <t>GB-CHC-1090745</t>
   </si>
   <si>
+    <t>National NGO</t>
+  </si>
+  <si>
     <t>22</t>
   </si>
   <si>
-    <t>National NGO</t>
-  </si>
-  <si>
     <t>GB-CHC-298316</t>
   </si>
   <si>
@@ -370,12 +370,12 @@
     <t>ZA-NPO-061-870</t>
   </si>
   <si>
+    <t>Regional NGO</t>
+  </si>
+  <si>
     <t>23</t>
   </si>
   <si>
-    <t>Regional NGO</t>
-  </si>
-  <si>
     <t>South Africa</t>
   </si>
   <si>
@@ -472,10 +472,10 @@
     <t>GB-COH-03788027</t>
   </si>
   <si>
+    <t>Private Sector</t>
+  </si>
+  <si>
     <t>70</t>
-  </si>
-  <si>
-    <t>Private Sector</t>
   </si>
   <si>
     <t>GB-CHC-1058991</t>

--- a/api/xlsx/fr/ReportingOrganisation.xlsx
+++ b/api/xlsx/fr/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6200" uniqueCount="1347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6210" uniqueCount="1349">
   <si>
     <t>code</t>
   </si>
@@ -3997,6 +3997,9 @@
     <t>XI-GRID-grid.7836.a</t>
   </si>
   <si>
+    <t>XI-IATI-KHF</t>
+  </si>
+  <si>
     <t>GB-CHC-1158838</t>
   </si>
   <si>
@@ -4046,6 +4049,9 @@
   </si>
   <si>
     <t>XM-DAC-47015</t>
+  </si>
+  <si>
+    <t>UG-RSB-197310</t>
   </si>
   <si>
     <t>ZM-PCR-12015013762</t>
@@ -4386,7 +4392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1240"/>
+  <dimension ref="A1:E1242"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25154,13 +25160,13 @@
         <v>6</v>
       </c>
       <c r="C1222" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D1222" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E1222" t="s">
-        <v>22</v>
+        <v>724</v>
       </c>
     </row>
     <row r="1223" spans="1:5">
@@ -25177,7 +25183,7 @@
         <v>21</v>
       </c>
       <c r="E1223" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1224" spans="1:5">
@@ -25194,7 +25200,7 @@
         <v>21</v>
       </c>
       <c r="E1224" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1225" spans="1:5">
@@ -25205,13 +25211,13 @@
         <v>6</v>
       </c>
       <c r="C1225" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="D1225" t="s">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="E1225" t="s">
-        <v>1177</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1226" spans="1:5">
@@ -25228,7 +25234,7 @@
         <v>80</v>
       </c>
       <c r="E1226" t="s">
-        <v>1312</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="1227" spans="1:5">
@@ -25239,13 +25245,13 @@
         <v>6</v>
       </c>
       <c r="C1227" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="D1227" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="E1227" t="s">
-        <v>22</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="1228" spans="1:5">
@@ -25256,13 +25262,13 @@
         <v>6</v>
       </c>
       <c r="C1228" t="s">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="D1228" t="s">
-        <v>153</v>
+        <v>21</v>
       </c>
       <c r="E1228" t="s">
-        <v>724</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1229" spans="1:5">
@@ -25273,13 +25279,13 @@
         <v>6</v>
       </c>
       <c r="C1229" t="s">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="D1229" t="s">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="E1229" t="s">
-        <v>430</v>
+        <v>724</v>
       </c>
     </row>
     <row r="1230" spans="1:5">
@@ -25296,7 +25302,7 @@
         <v>80</v>
       </c>
       <c r="E1230" t="s">
-        <v>17</v>
+        <v>430</v>
       </c>
     </row>
     <row r="1231" spans="1:5">
@@ -25307,13 +25313,13 @@
         <v>6</v>
       </c>
       <c r="C1231" t="s">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="D1231" t="s">
-        <v>153</v>
+        <v>80</v>
       </c>
       <c r="E1231" t="s">
-        <v>1312</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1232" spans="1:5">
@@ -25324,13 +25330,13 @@
         <v>6</v>
       </c>
       <c r="C1232" t="s">
-        <v>118</v>
+        <v>152</v>
       </c>
       <c r="D1232" t="s">
-        <v>119</v>
+        <v>153</v>
       </c>
       <c r="E1232" t="s">
-        <v>1177</v>
+        <v>1312</v>
       </c>
     </row>
     <row r="1233" spans="1:5">
@@ -25341,13 +25347,13 @@
         <v>6</v>
       </c>
       <c r="C1233" t="s">
-        <v>20</v>
+        <v>118</v>
       </c>
       <c r="D1233" t="s">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="E1233" t="s">
-        <v>230</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="1234" spans="1:5">
@@ -25358,13 +25364,13 @@
         <v>6</v>
       </c>
       <c r="C1234" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D1234" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E1234" t="s">
-        <v>44</v>
+        <v>230</v>
       </c>
     </row>
     <row r="1235" spans="1:5">
@@ -25375,13 +25381,13 @@
         <v>6</v>
       </c>
       <c r="C1235" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D1235" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="E1235" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
     </row>
     <row r="1236" spans="1:5">
@@ -25392,10 +25398,10 @@
         <v>6</v>
       </c>
       <c r="C1236" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D1236" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E1236" t="s">
         <v>22</v>
@@ -25409,13 +25415,13 @@
         <v>6</v>
       </c>
       <c r="C1237" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D1237" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
       <c r="E1237" t="s">
-        <v>724</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1238" spans="1:5">
@@ -25426,13 +25432,13 @@
         <v>6</v>
       </c>
       <c r="C1238" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="D1238" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="E1238" t="s">
-        <v>242</v>
+        <v>724</v>
       </c>
     </row>
     <row r="1239" spans="1:5">
@@ -25443,29 +25449,63 @@
         <v>6</v>
       </c>
       <c r="C1239" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D1239" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="E1239" t="s">
-        <v>1345</v>
+        <v>242</v>
       </c>
     </row>
     <row r="1240" spans="1:5">
       <c r="A1240" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B1240" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1240" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1240" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1240" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:5">
+      <c r="A1241" t="s">
         <v>1346</v>
       </c>
-      <c r="B1240" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1240" t="s">
+      <c r="B1241" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1241" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1241" t="s">
+        <v>80</v>
+      </c>
+      <c r="E1241" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:5">
+      <c r="A1242" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B1242" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1242" t="s">
         <v>24</v>
       </c>
-      <c r="D1240" t="s">
+      <c r="D1242" t="s">
         <v>25</v>
       </c>
-      <c r="E1240" t="s">
+      <c r="E1242" t="s">
         <v>17</v>
       </c>
     </row>

--- a/api/xlsx/fr/ReportingOrganisation.xlsx
+++ b/api/xlsx/fr/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6215" uniqueCount="1350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6225" uniqueCount="1352">
   <si>
     <t>code</t>
   </si>
@@ -22,78 +22,78 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:organisation-type-code</t>
+  </si>
+  <si>
+    <t>codeforiati:hq-country-or-region</t>
+  </si>
+  <si>
     <t>codeforiati:organisation-type</t>
   </si>
   <si>
-    <t>codeforiati:hq-country-or-region</t>
-  </si>
-  <si>
-    <t>codeforiati:organisation-type-code</t>
-  </si>
-  <si>
     <t>AU-5</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
     <t>Government</t>
   </si>
   <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>44000</t>
   </si>
   <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>(No country assigned)</t>
+  </si>
+  <si>
     <t>Multilateral</t>
   </si>
   <si>
-    <t>(No country assigned)</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>US-EIN-941655673</t>
   </si>
   <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
     <t>Foundation</t>
   </si>
   <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>41AAA</t>
   </si>
   <si>
     <t>GB-CHC-1038860</t>
   </si>
   <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
     <t>International NGO</t>
   </si>
   <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>XI-IATI-EC_DEVCO</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>Other Public Sector</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>SE-0</t>
   </si>
   <si>
@@ -163,12 +163,12 @@
     <t>47122</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>Public Private Partnership</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>US-EIN-300108263</t>
   </si>
   <si>
@@ -190,15 +190,15 @@
     <t>NP-CRO-45995/063/064</t>
   </si>
   <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>Nepal</t>
+  </si>
+  <si>
     <t>Academic, Training and Research</t>
   </si>
   <si>
-    <t>Nepal</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
     <t>GB-CHC-327421</t>
   </si>
   <si>
@@ -253,12 +253,12 @@
     <t>GB-CHC-1090745</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>National NGO</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>GB-CHC-298316</t>
   </si>
   <si>
@@ -370,15 +370,15 @@
     <t>ZA-NPO-061-870</t>
   </si>
   <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
     <t>Regional NGO</t>
   </si>
   <si>
-    <t>South Africa</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
     <t>30001</t>
   </si>
   <si>
@@ -472,12 +472,12 @@
     <t>GB-COH-03788027</t>
   </si>
   <si>
+    <t>70</t>
+  </si>
+  <si>
     <t>Private Sector</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>GB-CHC-1058991</t>
   </si>
   <si>
@@ -3748,6 +3748,9 @@
     <t>ZA-CIP-2007-0308903-08</t>
   </si>
   <si>
+    <t>GB-COH-06581421</t>
+  </si>
+  <si>
     <t>ML-NIF-055000335T</t>
   </si>
   <si>
@@ -3764,6 +3767,9 @@
   </si>
   <si>
     <t>GH-RGD-CG077262013</t>
+  </si>
+  <si>
+    <t>BD-NAB-2004</t>
   </si>
   <si>
     <t>XI-BRIDGE-1812689272</t>
@@ -4395,7 +4401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1243"/>
+  <dimension ref="A1:E1245"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -23786,13 +23792,13 @@
         <v>6</v>
       </c>
       <c r="C1141" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="D1141" t="s">
-        <v>680</v>
+        <v>21</v>
       </c>
       <c r="E1141" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1142" spans="1:5">
@@ -23806,7 +23812,7 @@
         <v>20</v>
       </c>
       <c r="D1142" t="s">
-        <v>44</v>
+        <v>680</v>
       </c>
       <c r="E1142" t="s">
         <v>22</v>
@@ -23823,7 +23829,7 @@
         <v>20</v>
       </c>
       <c r="D1143" t="s">
-        <v>188</v>
+        <v>44</v>
       </c>
       <c r="E1143" t="s">
         <v>22</v>
@@ -23840,7 +23846,7 @@
         <v>20</v>
       </c>
       <c r="D1144" t="s">
-        <v>242</v>
+        <v>188</v>
       </c>
       <c r="E1144" t="s">
         <v>22</v>
@@ -23857,7 +23863,7 @@
         <v>20</v>
       </c>
       <c r="D1145" t="s">
-        <v>27</v>
+        <v>242</v>
       </c>
       <c r="E1145" t="s">
         <v>22</v>
@@ -23871,13 +23877,13 @@
         <v>6</v>
       </c>
       <c r="C1146" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="D1146" t="s">
-        <v>267</v>
+        <v>27</v>
       </c>
       <c r="E1146" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1147" spans="1:5">
@@ -23888,13 +23894,13 @@
         <v>6</v>
       </c>
       <c r="C1147" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="D1147" t="s">
-        <v>16</v>
+        <v>267</v>
       </c>
       <c r="E1147" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1148" spans="1:5">
@@ -23905,13 +23911,13 @@
         <v>6</v>
       </c>
       <c r="C1148" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="D1148" t="s">
-        <v>16</v>
+        <v>430</v>
       </c>
       <c r="E1148" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1149" spans="1:5">
@@ -23922,13 +23928,13 @@
         <v>6</v>
       </c>
       <c r="C1149" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D1149" t="s">
-        <v>649</v>
+        <v>16</v>
       </c>
       <c r="E1149" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1150" spans="1:5">
@@ -23939,13 +23945,13 @@
         <v>6</v>
       </c>
       <c r="C1150" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="D1150" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E1150" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1151" spans="1:5">
@@ -23956,13 +23962,13 @@
         <v>6</v>
       </c>
       <c r="C1151" t="s">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="D1151" t="s">
-        <v>44</v>
+        <v>649</v>
       </c>
       <c r="E1151" t="s">
-        <v>153</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1152" spans="1:5">
@@ -23973,13 +23979,13 @@
         <v>6</v>
       </c>
       <c r="C1152" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="D1152" t="s">
-        <v>196</v>
+        <v>21</v>
       </c>
       <c r="E1152" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1153" spans="1:5">
@@ -23990,13 +23996,13 @@
         <v>6</v>
       </c>
       <c r="C1153" t="s">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="D1153" t="s">
-        <v>242</v>
+        <v>44</v>
       </c>
       <c r="E1153" t="s">
-        <v>22</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1154" spans="1:5">
@@ -24007,13 +24013,13 @@
         <v>6</v>
       </c>
       <c r="C1154" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="D1154" t="s">
-        <v>16</v>
+        <v>196</v>
       </c>
       <c r="E1154" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1155" spans="1:5">
@@ -24024,13 +24030,13 @@
         <v>6</v>
       </c>
       <c r="C1155" t="s">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="D1155" t="s">
-        <v>21</v>
+        <v>242</v>
       </c>
       <c r="E1155" t="s">
-        <v>153</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1156" spans="1:5">
@@ -24041,13 +24047,13 @@
         <v>6</v>
       </c>
       <c r="C1156" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="D1156" t="s">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="E1156" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1157" spans="1:5">
@@ -24058,13 +24064,13 @@
         <v>6</v>
       </c>
       <c r="C1157" t="s">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="D1157" t="s">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="E1157" t="s">
-        <v>22</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1158" spans="1:5">
@@ -24075,13 +24081,13 @@
         <v>6</v>
       </c>
       <c r="C1158" t="s">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="D1158" t="s">
-        <v>487</v>
+        <v>59</v>
       </c>
       <c r="E1158" t="s">
-        <v>153</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1159" spans="1:5">
@@ -24092,13 +24098,13 @@
         <v>6</v>
       </c>
       <c r="C1159" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="D1159" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="E1159" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1160" spans="1:5">
@@ -24109,13 +24115,13 @@
         <v>6</v>
       </c>
       <c r="C1160" t="s">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="D1160" t="s">
-        <v>213</v>
+        <v>487</v>
       </c>
       <c r="E1160" t="s">
-        <v>80</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1161" spans="1:5">
@@ -24126,13 +24132,13 @@
         <v>6</v>
       </c>
       <c r="C1161" t="s">
-        <v>11</v>
+        <v>58</v>
       </c>
       <c r="D1161" t="s">
-        <v>21</v>
+        <v>213</v>
       </c>
       <c r="E1161" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1162" spans="1:5">
@@ -24143,13 +24149,13 @@
         <v>6</v>
       </c>
       <c r="C1162" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="D1162" t="s">
-        <v>44</v>
+        <v>213</v>
       </c>
       <c r="E1162" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1163" spans="1:5">
@@ -24160,13 +24166,13 @@
         <v>6</v>
       </c>
       <c r="C1163" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="D1163" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="E1163" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1164" spans="1:5">
@@ -24177,13 +24183,13 @@
         <v>6</v>
       </c>
       <c r="C1164" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D1164" t="s">
-        <v>649</v>
+        <v>44</v>
       </c>
       <c r="E1164" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1165" spans="1:5">
@@ -24194,13 +24200,13 @@
         <v>6</v>
       </c>
       <c r="C1165" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="D1165" t="s">
-        <v>21</v>
+        <v>59</v>
       </c>
       <c r="E1165" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1166" spans="1:5">
@@ -24211,13 +24217,13 @@
         <v>6</v>
       </c>
       <c r="C1166" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="D1166" t="s">
-        <v>12</v>
+        <v>649</v>
       </c>
       <c r="E1166" t="s">
-        <v>13</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1167" spans="1:5">
@@ -24228,13 +24234,13 @@
         <v>6</v>
       </c>
       <c r="C1167" t="s">
-        <v>118</v>
+        <v>20</v>
       </c>
       <c r="D1167" t="s">
-        <v>230</v>
+        <v>21</v>
       </c>
       <c r="E1167" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1168" spans="1:5">
@@ -24245,13 +24251,13 @@
         <v>6</v>
       </c>
       <c r="C1168" t="s">
-        <v>79</v>
+        <v>11</v>
       </c>
       <c r="D1168" t="s">
-        <v>649</v>
+        <v>12</v>
       </c>
       <c r="E1168" t="s">
-        <v>80</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1169" spans="1:5">
@@ -24262,13 +24268,13 @@
         <v>6</v>
       </c>
       <c r="C1169" t="s">
-        <v>7</v>
+        <v>118</v>
       </c>
       <c r="D1169" t="s">
-        <v>649</v>
+        <v>230</v>
       </c>
       <c r="E1169" t="s">
-        <v>9</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1170" spans="1:5">
@@ -24279,13 +24285,13 @@
         <v>6</v>
       </c>
       <c r="C1170" t="s">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="D1170" t="s">
-        <v>724</v>
+        <v>649</v>
       </c>
       <c r="E1170" t="s">
-        <v>153</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1171" spans="1:5">
@@ -24296,13 +24302,13 @@
         <v>6</v>
       </c>
       <c r="C1171" t="s">
-        <v>152</v>
+        <v>7</v>
       </c>
       <c r="D1171" t="s">
-        <v>1233</v>
+        <v>649</v>
       </c>
       <c r="E1171" t="s">
-        <v>153</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1172" spans="1:5">
@@ -24313,13 +24319,13 @@
         <v>6</v>
       </c>
       <c r="C1172" t="s">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="D1172" t="s">
-        <v>29</v>
+        <v>724</v>
       </c>
       <c r="E1172" t="s">
-        <v>80</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1173" spans="1:5">
@@ -24330,13 +24336,13 @@
         <v>6</v>
       </c>
       <c r="C1173" t="s">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="D1173" t="s">
-        <v>948</v>
+        <v>1233</v>
       </c>
       <c r="E1173" t="s">
-        <v>80</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1174" spans="1:5">
@@ -24347,13 +24353,13 @@
         <v>6</v>
       </c>
       <c r="C1174" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="D1174" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E1174" t="s">
-        <v>50</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1175" spans="1:5">
@@ -24364,13 +24370,13 @@
         <v>6</v>
       </c>
       <c r="C1175" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="D1175" t="s">
-        <v>16</v>
+        <v>948</v>
       </c>
       <c r="E1175" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1176" spans="1:5">
@@ -24381,13 +24387,13 @@
         <v>6</v>
       </c>
       <c r="C1176" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="D1176" t="s">
-        <v>213</v>
+        <v>38</v>
       </c>
       <c r="E1176" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1177" spans="1:5">
@@ -24398,13 +24404,13 @@
         <v>6</v>
       </c>
       <c r="C1177" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="D1177" t="s">
-        <v>859</v>
+        <v>16</v>
       </c>
       <c r="E1177" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1178" spans="1:5">
@@ -24415,13 +24421,13 @@
         <v>6</v>
       </c>
       <c r="C1178" t="s">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="D1178" t="s">
-        <v>44</v>
+        <v>213</v>
       </c>
       <c r="E1178" t="s">
-        <v>153</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1179" spans="1:5">
@@ -24432,13 +24438,13 @@
         <v>6</v>
       </c>
       <c r="C1179" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="D1179" t="s">
-        <v>44</v>
+        <v>859</v>
       </c>
       <c r="E1179" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1180" spans="1:5">
@@ -24449,13 +24455,13 @@
         <v>6</v>
       </c>
       <c r="C1180" t="s">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="D1180" t="s">
-        <v>948</v>
+        <v>44</v>
       </c>
       <c r="E1180" t="s">
-        <v>80</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1181" spans="1:5">
@@ -24466,13 +24472,13 @@
         <v>6</v>
       </c>
       <c r="C1181" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D1181" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E1181" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1182" spans="1:5">
@@ -24483,13 +24489,13 @@
         <v>6</v>
       </c>
       <c r="C1182" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="D1182" t="s">
-        <v>44</v>
+        <v>948</v>
       </c>
       <c r="E1182" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1183" spans="1:5">
@@ -24503,7 +24509,7 @@
         <v>20</v>
       </c>
       <c r="D1183" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="E1183" t="s">
         <v>22</v>
@@ -24520,7 +24526,7 @@
         <v>20</v>
       </c>
       <c r="D1184" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E1184" t="s">
         <v>22</v>
@@ -24534,13 +24540,13 @@
         <v>6</v>
       </c>
       <c r="C1185" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="D1185" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="E1185" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1186" spans="1:5">
@@ -24554,7 +24560,7 @@
         <v>20</v>
       </c>
       <c r="D1186" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E1186" t="s">
         <v>22</v>
@@ -24568,13 +24574,13 @@
         <v>6</v>
       </c>
       <c r="C1187" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="D1187" t="s">
         <v>44</v>
       </c>
       <c r="E1187" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1188" spans="1:5">
@@ -24588,7 +24594,7 @@
         <v>20</v>
       </c>
       <c r="D1188" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E1188" t="s">
         <v>22</v>
@@ -24602,13 +24608,13 @@
         <v>6</v>
       </c>
       <c r="C1189" t="s">
-        <v>152</v>
+        <v>15</v>
       </c>
       <c r="D1189" t="s">
         <v>44</v>
       </c>
       <c r="E1189" t="s">
-        <v>153</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1190" spans="1:5">
@@ -24622,7 +24628,7 @@
         <v>20</v>
       </c>
       <c r="D1190" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="E1190" t="s">
         <v>22</v>
@@ -24636,13 +24642,13 @@
         <v>6</v>
       </c>
       <c r="C1191" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="D1191" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E1191" t="s">
-        <v>17</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1192" spans="1:5">
@@ -24653,13 +24659,13 @@
         <v>6</v>
       </c>
       <c r="C1192" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D1192" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E1192" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1193" spans="1:5">
@@ -24670,13 +24676,13 @@
         <v>6</v>
       </c>
       <c r="C1193" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D1193" t="s">
         <v>21</v>
       </c>
       <c r="E1193" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1194" spans="1:5">
@@ -24687,13 +24693,13 @@
         <v>6</v>
       </c>
       <c r="C1194" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D1194" t="s">
         <v>21</v>
       </c>
       <c r="E1194" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1195" spans="1:5">
@@ -24704,13 +24710,13 @@
         <v>6</v>
       </c>
       <c r="C1195" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="D1195" t="s">
         <v>21</v>
       </c>
       <c r="E1195" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1196" spans="1:5">
@@ -24738,13 +24744,13 @@
         <v>6</v>
       </c>
       <c r="C1197" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="D1197" t="s">
         <v>21</v>
       </c>
       <c r="E1197" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1198" spans="1:5">
@@ -24755,13 +24761,13 @@
         <v>6</v>
       </c>
       <c r="C1198" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="D1198" t="s">
         <v>21</v>
       </c>
       <c r="E1198" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1199" spans="1:5">
@@ -24772,13 +24778,13 @@
         <v>6</v>
       </c>
       <c r="C1199" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D1199" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E1199" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1200" spans="1:5">
@@ -24789,13 +24795,13 @@
         <v>6</v>
       </c>
       <c r="C1200" t="s">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="D1200" t="s">
         <v>21</v>
       </c>
       <c r="E1200" t="s">
-        <v>153</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1201" spans="1:5">
@@ -24806,13 +24812,13 @@
         <v>6</v>
       </c>
       <c r="C1201" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D1201" t="s">
         <v>16</v>
       </c>
       <c r="E1201" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1202" spans="1:5">
@@ -24823,13 +24829,13 @@
         <v>6</v>
       </c>
       <c r="C1202" t="s">
-        <v>58</v>
+        <v>152</v>
       </c>
       <c r="D1202" t="s">
         <v>21</v>
       </c>
       <c r="E1202" t="s">
-        <v>60</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1203" spans="1:5">
@@ -24840,13 +24846,13 @@
         <v>6</v>
       </c>
       <c r="C1203" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="D1203" t="s">
-        <v>680</v>
+        <v>16</v>
       </c>
       <c r="E1203" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1204" spans="1:5">
@@ -24874,13 +24880,13 @@
         <v>6</v>
       </c>
       <c r="C1205" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="D1205" t="s">
-        <v>29</v>
+        <v>680</v>
       </c>
       <c r="E1205" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1206" spans="1:5">
@@ -24891,13 +24897,13 @@
         <v>6</v>
       </c>
       <c r="C1206" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D1206" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E1206" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1207" spans="1:5">
@@ -24908,13 +24914,13 @@
         <v>6</v>
       </c>
       <c r="C1207" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="D1207" t="s">
-        <v>948</v>
+        <v>29</v>
       </c>
       <c r="E1207" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1208" spans="1:5">
@@ -24925,18 +24931,18 @@
         <v>6</v>
       </c>
       <c r="C1208" t="s">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="D1208" t="s">
-        <v>1312</v>
+        <v>44</v>
       </c>
       <c r="E1208" t="s">
-        <v>80</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1209" spans="1:5">
       <c r="A1209" t="s">
-        <v>1313</v>
+        <v>1312</v>
       </c>
       <c r="B1209" t="s">
         <v>6</v>
@@ -24945,7 +24951,7 @@
         <v>79</v>
       </c>
       <c r="D1209" t="s">
-        <v>724</v>
+        <v>948</v>
       </c>
       <c r="E1209" t="s">
         <v>80</v>
@@ -24953,16 +24959,16 @@
     </row>
     <row r="1210" spans="1:5">
       <c r="A1210" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B1210" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1210" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1210" t="s">
         <v>1314</v>
-      </c>
-      <c r="B1210" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1210" t="s">
-        <v>79</v>
-      </c>
-      <c r="D1210" t="s">
-        <v>1177</v>
       </c>
       <c r="E1210" t="s">
         <v>80</v>
@@ -24976,13 +24982,13 @@
         <v>6</v>
       </c>
       <c r="C1211" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="D1211" t="s">
-        <v>16</v>
+        <v>724</v>
       </c>
       <c r="E1211" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1212" spans="1:5">
@@ -24993,18 +24999,18 @@
         <v>6</v>
       </c>
       <c r="C1212" t="s">
-        <v>15</v>
+        <v>79</v>
       </c>
       <c r="D1212" t="s">
-        <v>1317</v>
+        <v>1177</v>
       </c>
       <c r="E1212" t="s">
-        <v>17</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1213" spans="1:5">
       <c r="A1213" t="s">
-        <v>1318</v>
+        <v>1317</v>
       </c>
       <c r="B1213" t="s">
         <v>6</v>
@@ -25013,7 +25019,7 @@
         <v>20</v>
       </c>
       <c r="D1213" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E1213" t="s">
         <v>22</v>
@@ -25021,19 +25027,19 @@
     </row>
     <row r="1214" spans="1:5">
       <c r="A1214" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B1214" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1214" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1214" t="s">
         <v>1319</v>
       </c>
-      <c r="B1214" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1214" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1214" t="s">
-        <v>21</v>
-      </c>
       <c r="E1214" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1215" spans="1:5">
@@ -25044,13 +25050,13 @@
         <v>6</v>
       </c>
       <c r="C1215" t="s">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="D1215" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E1215" t="s">
-        <v>153</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1216" spans="1:5">
@@ -25061,13 +25067,13 @@
         <v>6</v>
       </c>
       <c r="C1216" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="D1216" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="E1216" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1217" spans="1:5">
@@ -25078,13 +25084,13 @@
         <v>6</v>
       </c>
       <c r="C1217" t="s">
-        <v>7</v>
+        <v>152</v>
       </c>
       <c r="D1217" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E1217" t="s">
-        <v>9</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1218" spans="1:5">
@@ -25098,7 +25104,7 @@
         <v>20</v>
       </c>
       <c r="D1218" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E1218" t="s">
         <v>22</v>
@@ -25112,13 +25118,13 @@
         <v>6</v>
       </c>
       <c r="C1219" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D1219" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E1219" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1220" spans="1:5">
@@ -25129,13 +25135,13 @@
         <v>6</v>
       </c>
       <c r="C1220" t="s">
-        <v>152</v>
+        <v>20</v>
       </c>
       <c r="D1220" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="E1220" t="s">
-        <v>153</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1221" spans="1:5">
@@ -25146,13 +25152,13 @@
         <v>6</v>
       </c>
       <c r="C1221" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="D1221" t="s">
-        <v>119</v>
+        <v>16</v>
       </c>
       <c r="E1221" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1222" spans="1:5">
@@ -25163,13 +25169,13 @@
         <v>6</v>
       </c>
       <c r="C1222" t="s">
-        <v>15</v>
+        <v>152</v>
       </c>
       <c r="D1222" t="s">
-        <v>724</v>
+        <v>21</v>
       </c>
       <c r="E1222" t="s">
-        <v>17</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1223" spans="1:5">
@@ -25180,13 +25186,13 @@
         <v>6</v>
       </c>
       <c r="C1223" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="D1223" t="s">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="E1223" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1224" spans="1:5">
@@ -25197,13 +25203,13 @@
         <v>6</v>
       </c>
       <c r="C1224" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D1224" t="s">
-        <v>29</v>
+        <v>724</v>
       </c>
       <c r="E1224" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1225" spans="1:5">
@@ -25231,13 +25237,13 @@
         <v>6</v>
       </c>
       <c r="C1226" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="D1226" t="s">
-        <v>1177</v>
+        <v>29</v>
       </c>
       <c r="E1226" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1227" spans="1:5">
@@ -25248,13 +25254,13 @@
         <v>6</v>
       </c>
       <c r="C1227" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="D1227" t="s">
-        <v>1312</v>
+        <v>21</v>
       </c>
       <c r="E1227" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1228" spans="1:5">
@@ -25265,13 +25271,13 @@
         <v>6</v>
       </c>
       <c r="C1228" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="D1228" t="s">
-        <v>21</v>
+        <v>1177</v>
       </c>
       <c r="E1228" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1229" spans="1:5">
@@ -25282,13 +25288,13 @@
         <v>6</v>
       </c>
       <c r="C1229" t="s">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="D1229" t="s">
-        <v>724</v>
+        <v>1314</v>
       </c>
       <c r="E1229" t="s">
-        <v>153</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1230" spans="1:5">
@@ -25299,13 +25305,13 @@
         <v>6</v>
       </c>
       <c r="C1230" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="D1230" t="s">
-        <v>430</v>
+        <v>21</v>
       </c>
       <c r="E1230" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1231" spans="1:5">
@@ -25316,13 +25322,13 @@
         <v>6</v>
       </c>
       <c r="C1231" t="s">
-        <v>79</v>
+        <v>152</v>
       </c>
       <c r="D1231" t="s">
-        <v>16</v>
+        <v>724</v>
       </c>
       <c r="E1231" t="s">
-        <v>80</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1232" spans="1:5">
@@ -25333,13 +25339,13 @@
         <v>6</v>
       </c>
       <c r="C1232" t="s">
-        <v>152</v>
+        <v>79</v>
       </c>
       <c r="D1232" t="s">
-        <v>1312</v>
+        <v>430</v>
       </c>
       <c r="E1232" t="s">
-        <v>153</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1233" spans="1:5">
@@ -25350,13 +25356,13 @@
         <v>6</v>
       </c>
       <c r="C1233" t="s">
-        <v>118</v>
+        <v>79</v>
       </c>
       <c r="D1233" t="s">
-        <v>1177</v>
+        <v>16</v>
       </c>
       <c r="E1233" t="s">
-        <v>120</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1234" spans="1:5">
@@ -25367,13 +25373,13 @@
         <v>6</v>
       </c>
       <c r="C1234" t="s">
-        <v>20</v>
+        <v>152</v>
       </c>
       <c r="D1234" t="s">
-        <v>230</v>
+        <v>1314</v>
       </c>
       <c r="E1234" t="s">
-        <v>22</v>
+        <v>153</v>
       </c>
     </row>
     <row r="1235" spans="1:5">
@@ -25384,13 +25390,13 @@
         <v>6</v>
       </c>
       <c r="C1235" t="s">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="D1235" t="s">
-        <v>44</v>
+        <v>1177</v>
       </c>
       <c r="E1235" t="s">
-        <v>25</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1236" spans="1:5">
@@ -25404,7 +25410,7 @@
         <v>20</v>
       </c>
       <c r="D1236" t="s">
-        <v>21</v>
+        <v>230</v>
       </c>
       <c r="E1236" t="s">
         <v>22</v>
@@ -25421,7 +25427,7 @@
         <v>24</v>
       </c>
       <c r="D1237" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E1237" t="s">
         <v>25</v>
@@ -25435,13 +25441,13 @@
         <v>6</v>
       </c>
       <c r="C1238" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="D1238" t="s">
-        <v>724</v>
+        <v>21</v>
       </c>
       <c r="E1238" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1239" spans="1:5">
@@ -25452,13 +25458,13 @@
         <v>6</v>
       </c>
       <c r="C1239" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D1239" t="s">
-        <v>242</v>
+        <v>21</v>
       </c>
       <c r="E1239" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1240" spans="1:5">
@@ -25472,7 +25478,7 @@
         <v>79</v>
       </c>
       <c r="D1240" t="s">
-        <v>213</v>
+        <v>724</v>
       </c>
       <c r="E1240" t="s">
         <v>80</v>
@@ -25486,46 +25492,80 @@
         <v>6</v>
       </c>
       <c r="C1241" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D1241" t="s">
-        <v>1347</v>
+        <v>242</v>
       </c>
       <c r="E1241" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1242" spans="1:5">
       <c r="A1242" t="s">
-        <v>1348</v>
+        <v>1347</v>
       </c>
       <c r="B1242" t="s">
         <v>6</v>
       </c>
       <c r="C1242" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="D1242" t="s">
-        <v>16</v>
+        <v>213</v>
       </c>
       <c r="E1242" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1243" spans="1:5">
       <c r="A1243" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B1243" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1243" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1243" t="s">
         <v>1349</v>
       </c>
-      <c r="B1243" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1243" t="s">
+      <c r="E1243" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:5">
+      <c r="A1244" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B1244" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1244" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1244" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1244" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:5">
+      <c r="A1245" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B1245" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1245" t="s">
         <v>58</v>
       </c>
-      <c r="D1243" t="s">
+      <c r="D1245" t="s">
         <v>16</v>
       </c>
-      <c r="E1243" t="s">
+      <c r="E1245" t="s">
         <v>60</v>
       </c>
     </row>

--- a/api/xlsx/fr/ReportingOrganisation.xlsx
+++ b/api/xlsx/fr/ReportingOrganisation.xlsx
@@ -22,78 +22,78 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:organisation-type</t>
+  </si>
+  <si>
+    <t>codeforiati:hq-country-or-region</t>
+  </si>
+  <si>
     <t>codeforiati:organisation-type-code</t>
   </si>
   <si>
-    <t>codeforiati:hq-country-or-region</t>
-  </si>
-  <si>
-    <t>codeforiati:organisation-type</t>
-  </si>
-  <si>
     <t>AU-5</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>Government</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>Government</t>
-  </si>
-  <si>
     <t>44000</t>
   </si>
   <si>
+    <t>Multilateral</t>
+  </si>
+  <si>
+    <t>(No country assigned)</t>
+  </si>
+  <si>
     <t>40</t>
   </si>
   <si>
-    <t>(No country assigned)</t>
-  </si>
-  <si>
-    <t>Multilateral</t>
-  </si>
-  <si>
     <t>US-EIN-941655673</t>
   </si>
   <si>
+    <t>Foundation</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
     <t>60</t>
   </si>
   <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>Foundation</t>
-  </si>
-  <si>
     <t>41AAA</t>
   </si>
   <si>
     <t>GB-CHC-1038860</t>
   </si>
   <si>
+    <t>International NGO</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
     <t>21</t>
   </si>
   <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>International NGO</t>
-  </si>
-  <si>
     <t>XI-IATI-EC_DEVCO</t>
   </si>
   <si>
+    <t>Other Public Sector</t>
+  </si>
+  <si>
     <t>15</t>
   </si>
   <si>
-    <t>Other Public Sector</t>
-  </si>
-  <si>
     <t>SE-0</t>
   </si>
   <si>
@@ -163,12 +163,12 @@
     <t>47122</t>
   </si>
   <si>
+    <t>Public Private Partnership</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
-    <t>Public Private Partnership</t>
-  </si>
-  <si>
     <t>US-EIN-300108263</t>
   </si>
   <si>
@@ -190,15 +190,15 @@
     <t>NP-CRO-45995/063/064</t>
   </si>
   <si>
+    <t>Academic, Training and Research</t>
+  </si>
+  <si>
+    <t>Nepal</t>
+  </si>
+  <si>
     <t>80</t>
   </si>
   <si>
-    <t>Nepal</t>
-  </si>
-  <si>
-    <t>Academic, Training and Research</t>
-  </si>
-  <si>
     <t>GB-CHC-327421</t>
   </si>
   <si>
@@ -253,12 +253,12 @@
     <t>GB-CHC-1090745</t>
   </si>
   <si>
+    <t>National NGO</t>
+  </si>
+  <si>
     <t>22</t>
   </si>
   <si>
-    <t>National NGO</t>
-  </si>
-  <si>
     <t>GB-CHC-298316</t>
   </si>
   <si>
@@ -370,15 +370,15 @@
     <t>ZA-NPO-061-870</t>
   </si>
   <si>
+    <t>Regional NGO</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
     <t>23</t>
   </si>
   <si>
-    <t>South Africa</t>
-  </si>
-  <si>
-    <t>Regional NGO</t>
-  </si>
-  <si>
     <t>30001</t>
   </si>
   <si>
@@ -472,10 +472,10 @@
     <t>GB-COH-03788027</t>
   </si>
   <si>
+    <t>Private Sector</t>
+  </si>
+  <si>
     <t>70</t>
-  </si>
-  <si>
-    <t>Private Sector</t>
   </si>
   <si>
     <t>GB-CHC-1058991</t>

--- a/api/xlsx/fr/ReportingOrganisation.xlsx
+++ b/api/xlsx/fr/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6305" uniqueCount="1372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6310" uniqueCount="1373">
   <si>
     <t>code</t>
   </si>
@@ -3995,6 +3995,9 @@
   </si>
   <si>
     <t>ID-KHH-5018112631240040</t>
+  </si>
+  <si>
+    <t>GB-CHC-1076722</t>
   </si>
   <si>
     <t>US-EIN-81-2339233</t>
@@ -4461,7 +4464,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1261"/>
+  <dimension ref="A1:E1262"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25229,13 +25232,13 @@
         <v>6</v>
       </c>
       <c r="C1222" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="D1222" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E1222" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1223" spans="1:5">
@@ -25246,30 +25249,30 @@
         <v>6</v>
       </c>
       <c r="C1223" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D1223" t="s">
-        <v>1329</v>
+        <v>16</v>
       </c>
       <c r="E1223" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1224" spans="1:5">
       <c r="A1224" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B1224" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1224" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1224" t="s">
         <v>1330</v>
       </c>
-      <c r="B1224" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1224" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1224" t="s">
-        <v>21</v>
-      </c>
       <c r="E1224" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1225" spans="1:5">
@@ -25280,13 +25283,13 @@
         <v>6</v>
       </c>
       <c r="C1225" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="D1225" t="s">
         <v>21</v>
       </c>
       <c r="E1225" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1226" spans="1:5">
@@ -25297,13 +25300,13 @@
         <v>6</v>
       </c>
       <c r="C1226" t="s">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="D1226" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E1226" t="s">
-        <v>155</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1227" spans="1:5">
@@ -25314,13 +25317,13 @@
         <v>6</v>
       </c>
       <c r="C1227" t="s">
-        <v>20</v>
+        <v>154</v>
       </c>
       <c r="D1227" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="E1227" t="s">
-        <v>22</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1228" spans="1:5">
@@ -25331,13 +25334,13 @@
         <v>6</v>
       </c>
       <c r="C1228" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D1228" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="E1228" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1229" spans="1:5">
@@ -25348,13 +25351,13 @@
         <v>6</v>
       </c>
       <c r="C1229" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D1229" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="E1229" t="s">
-        <v>22</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1230" spans="1:5">
@@ -25368,7 +25371,7 @@
         <v>20</v>
       </c>
       <c r="D1230" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E1230" t="s">
         <v>22</v>
@@ -25382,13 +25385,13 @@
         <v>6</v>
       </c>
       <c r="C1231" t="s">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="D1231" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="E1231" t="s">
-        <v>155</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1232" spans="1:5">
@@ -25399,13 +25402,13 @@
         <v>6</v>
       </c>
       <c r="C1232" t="s">
-        <v>58</v>
+        <v>154</v>
       </c>
       <c r="D1232" t="s">
-        <v>119</v>
+        <v>21</v>
       </c>
       <c r="E1232" t="s">
-        <v>60</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1233" spans="1:5">
@@ -25416,13 +25419,13 @@
         <v>6</v>
       </c>
       <c r="C1233" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="D1233" t="s">
-        <v>278</v>
+        <v>119</v>
       </c>
       <c r="E1233" t="s">
-        <v>17</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1234" spans="1:5">
@@ -25433,13 +25436,13 @@
         <v>6</v>
       </c>
       <c r="C1234" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="D1234" t="s">
-        <v>21</v>
+        <v>278</v>
       </c>
       <c r="E1234" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1235" spans="1:5">
@@ -25450,13 +25453,13 @@
         <v>6</v>
       </c>
       <c r="C1235" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="D1235" t="s">
         <v>21</v>
       </c>
       <c r="E1235" t="s">
-        <v>22</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1236" spans="1:5">
@@ -25470,7 +25473,7 @@
         <v>20</v>
       </c>
       <c r="D1236" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="E1236" t="s">
         <v>22</v>
@@ -25487,7 +25490,7 @@
         <v>20</v>
       </c>
       <c r="D1237" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="E1237" t="s">
         <v>22</v>
@@ -25501,13 +25504,13 @@
         <v>6</v>
       </c>
       <c r="C1238" t="s">
-        <v>79</v>
+        <v>20</v>
       </c>
       <c r="D1238" t="s">
-        <v>1184</v>
+        <v>21</v>
       </c>
       <c r="E1238" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1239" spans="1:5">
@@ -25521,7 +25524,7 @@
         <v>79</v>
       </c>
       <c r="D1239" t="s">
-        <v>1323</v>
+        <v>1184</v>
       </c>
       <c r="E1239" t="s">
         <v>80</v>
@@ -25535,13 +25538,13 @@
         <v>6</v>
       </c>
       <c r="C1240" t="s">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="D1240" t="s">
-        <v>21</v>
+        <v>1323</v>
       </c>
       <c r="E1240" t="s">
-        <v>22</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1241" spans="1:5">
@@ -25552,13 +25555,13 @@
         <v>6</v>
       </c>
       <c r="C1241" t="s">
-        <v>154</v>
+        <v>20</v>
       </c>
       <c r="D1241" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="E1241" t="s">
-        <v>155</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1242" spans="1:5">
@@ -25569,13 +25572,13 @@
         <v>6</v>
       </c>
       <c r="C1242" t="s">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="D1242" t="s">
-        <v>435</v>
+        <v>278</v>
       </c>
       <c r="E1242" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1243" spans="1:5">
@@ -25589,7 +25592,7 @@
         <v>79</v>
       </c>
       <c r="D1243" t="s">
-        <v>16</v>
+        <v>435</v>
       </c>
       <c r="E1243" t="s">
         <v>80</v>
@@ -25603,13 +25606,13 @@
         <v>6</v>
       </c>
       <c r="C1244" t="s">
-        <v>154</v>
+        <v>79</v>
       </c>
       <c r="D1244" t="s">
-        <v>1323</v>
+        <v>16</v>
       </c>
       <c r="E1244" t="s">
-        <v>155</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1245" spans="1:5">
@@ -25620,13 +25623,13 @@
         <v>6</v>
       </c>
       <c r="C1245" t="s">
-        <v>118</v>
+        <v>154</v>
       </c>
       <c r="D1245" t="s">
-        <v>1184</v>
+        <v>1323</v>
       </c>
       <c r="E1245" t="s">
-        <v>120</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1246" spans="1:5">
@@ -25637,13 +25640,13 @@
         <v>6</v>
       </c>
       <c r="C1246" t="s">
-        <v>20</v>
+        <v>118</v>
       </c>
       <c r="D1246" t="s">
-        <v>232</v>
+        <v>1184</v>
       </c>
       <c r="E1246" t="s">
-        <v>22</v>
+        <v>120</v>
       </c>
     </row>
     <row r="1247" spans="1:5">
@@ -25654,13 +25657,13 @@
         <v>6</v>
       </c>
       <c r="C1247" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D1247" t="s">
-        <v>44</v>
+        <v>232</v>
       </c>
       <c r="E1247" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1248" spans="1:5">
@@ -25671,13 +25674,13 @@
         <v>6</v>
       </c>
       <c r="C1248" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="D1248" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="E1248" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1249" spans="1:5">
@@ -25688,13 +25691,13 @@
         <v>6</v>
       </c>
       <c r="C1249" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D1249" t="s">
         <v>21</v>
       </c>
       <c r="E1249" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1250" spans="1:5">
@@ -25705,13 +25708,13 @@
         <v>6</v>
       </c>
       <c r="C1250" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="D1250" t="s">
-        <v>278</v>
+        <v>21</v>
       </c>
       <c r="E1250" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1251" spans="1:5">
@@ -25722,13 +25725,13 @@
         <v>6</v>
       </c>
       <c r="C1251" t="s">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c r="D1251" t="s">
-        <v>21</v>
+        <v>278</v>
       </c>
       <c r="E1251" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1252" spans="1:5">
@@ -25742,7 +25745,7 @@
         <v>58</v>
       </c>
       <c r="D1252" t="s">
-        <v>244</v>
+        <v>21</v>
       </c>
       <c r="E1252" t="s">
         <v>60</v>
@@ -25756,13 +25759,13 @@
         <v>6</v>
       </c>
       <c r="C1253" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="D1253" t="s">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="E1253" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1254" spans="1:5">
@@ -25776,7 +25779,7 @@
         <v>79</v>
       </c>
       <c r="D1254" t="s">
-        <v>1361</v>
+        <v>215</v>
       </c>
       <c r="E1254" t="s">
         <v>80</v>
@@ -25784,19 +25787,19 @@
     </row>
     <row r="1255" spans="1:5">
       <c r="A1255" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B1255" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1255" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1255" t="s">
         <v>1362</v>
       </c>
-      <c r="B1255" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1255" t="s">
-        <v>58</v>
-      </c>
-      <c r="D1255" t="s">
-        <v>21</v>
-      </c>
       <c r="E1255" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1256" spans="1:5">
@@ -25807,13 +25810,13 @@
         <v>6</v>
       </c>
       <c r="C1256" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="D1256" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E1256" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1257" spans="1:5">
@@ -25824,13 +25827,13 @@
         <v>6</v>
       </c>
       <c r="C1257" t="s">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="D1257" t="s">
         <v>16</v>
       </c>
       <c r="E1257" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1258" spans="1:5">
@@ -25841,44 +25844,44 @@
         <v>6</v>
       </c>
       <c r="C1258" t="s">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="D1258" t="s">
-        <v>1366</v>
+        <v>16</v>
       </c>
       <c r="E1258" t="s">
-        <v>155</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1259" spans="1:5">
       <c r="A1259" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B1259" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1259" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1259" t="s">
         <v>1367</v>
       </c>
-      <c r="B1259" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1259" t="s">
-        <v>79</v>
-      </c>
-      <c r="D1259" t="s">
-        <v>1368</v>
-      </c>
       <c r="E1259" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1260" spans="1:5">
       <c r="A1260" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B1260" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1260" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1260" t="s">
         <v>1369</v>
-      </c>
-      <c r="B1260" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1260" t="s">
-        <v>79</v>
-      </c>
-      <c r="D1260" t="s">
-        <v>1370</v>
       </c>
       <c r="E1260" t="s">
         <v>80</v>
@@ -25886,18 +25889,35 @@
     </row>
     <row r="1261" spans="1:5">
       <c r="A1261" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B1261" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1261" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1261" t="s">
         <v>1371</v>
       </c>
-      <c r="B1261" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1261" t="s">
+      <c r="E1261" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:5">
+      <c r="A1262" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B1262" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1262" t="s">
         <v>24</v>
       </c>
-      <c r="D1261" t="s">
+      <c r="D1262" t="s">
         <v>244</v>
       </c>
-      <c r="E1261" t="s">
+      <c r="E1262" t="s">
         <v>25</v>
       </c>
     </row>

--- a/api/xlsx/fr/ReportingOrganisation.xlsx
+++ b/api/xlsx/fr/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6310" uniqueCount="1373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6315" uniqueCount="1374">
   <si>
     <t>code</t>
   </si>
@@ -22,78 +22,78 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:organisation-type-code</t>
+  </si>
+  <si>
+    <t>codeforiati:hq-country-or-region</t>
+  </si>
+  <si>
     <t>codeforiati:organisation-type</t>
   </si>
   <si>
-    <t>codeforiati:hq-country-or-region</t>
-  </si>
-  <si>
-    <t>codeforiati:organisation-type-code</t>
-  </si>
-  <si>
     <t>AU-5</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
     <t>Government</t>
   </si>
   <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>44000</t>
   </si>
   <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>(No country assigned)</t>
+  </si>
+  <si>
     <t>Multilateral</t>
   </si>
   <si>
-    <t>(No country assigned)</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>US-EIN-941655673</t>
   </si>
   <si>
+    <t>60</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
     <t>Foundation</t>
   </si>
   <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>41AAA</t>
   </si>
   <si>
     <t>GB-CHC-1038860</t>
   </si>
   <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
     <t>International NGO</t>
   </si>
   <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>XI-IATI-EC_DEVCO</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>Other Public Sector</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>SE-0</t>
   </si>
   <si>
@@ -163,12 +163,12 @@
     <t>47122</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>Public Private Partnership</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>US-EIN-300108263</t>
   </si>
   <si>
@@ -190,15 +190,15 @@
     <t>NP-CRO-45995/063/064</t>
   </si>
   <si>
+    <t>80</t>
+  </si>
+  <si>
+    <t>Nepal</t>
+  </si>
+  <si>
     <t>Academic, Training and Research</t>
   </si>
   <si>
-    <t>Nepal</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
     <t>GB-CHC-327421</t>
   </si>
   <si>
@@ -253,12 +253,12 @@
     <t>GB-CHC-1090745</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>National NGO</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>GB-CHC-298316</t>
   </si>
   <si>
@@ -370,15 +370,15 @@
     <t>ZA-NPO-061-870</t>
   </si>
   <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
     <t>Regional NGO</t>
   </si>
   <si>
-    <t>South Africa</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
     <t>CH-FDJP-CHE-110347351</t>
   </si>
   <si>
@@ -478,12 +478,12 @@
     <t>GB-COH-03788027</t>
   </si>
   <si>
+    <t>70</t>
+  </si>
+  <si>
     <t>Private Sector</t>
   </si>
   <si>
-    <t>70</t>
-  </si>
-  <si>
     <t>GB-CHC-1058991</t>
   </si>
   <si>
@@ -4109,6 +4109,9 @@
   </si>
   <si>
     <t>XM-DAC-41149</t>
+  </si>
+  <si>
+    <t>GB-COH-02871809</t>
   </si>
   <si>
     <t>US-EIN-042103594</t>
@@ -4464,7 +4467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1262"/>
+  <dimension ref="A1:E1263"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25844,13 +25847,13 @@
         <v>6</v>
       </c>
       <c r="C1258" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="D1258" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E1258" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1259" spans="1:5">
@@ -25861,44 +25864,44 @@
         <v>6</v>
       </c>
       <c r="C1259" t="s">
-        <v>154</v>
+        <v>58</v>
       </c>
       <c r="D1259" t="s">
-        <v>1367</v>
+        <v>16</v>
       </c>
       <c r="E1259" t="s">
-        <v>155</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1260" spans="1:5">
       <c r="A1260" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B1260" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1260" t="s">
+        <v>154</v>
+      </c>
+      <c r="D1260" t="s">
         <v>1368</v>
       </c>
-      <c r="B1260" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1260" t="s">
-        <v>79</v>
-      </c>
-      <c r="D1260" t="s">
-        <v>1369</v>
-      </c>
       <c r="E1260" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1261" spans="1:5">
       <c r="A1261" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B1261" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1261" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1261" t="s">
         <v>1370</v>
-      </c>
-      <c r="B1261" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1261" t="s">
-        <v>79</v>
-      </c>
-      <c r="D1261" t="s">
-        <v>1371</v>
       </c>
       <c r="E1261" t="s">
         <v>80</v>
@@ -25906,18 +25909,35 @@
     </row>
     <row r="1262" spans="1:5">
       <c r="A1262" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B1262" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1262" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1262" t="s">
         <v>1372</v>
       </c>
-      <c r="B1262" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1262" t="s">
+      <c r="E1262" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:5">
+      <c r="A1263" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B1263" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1263" t="s">
         <v>24</v>
       </c>
-      <c r="D1262" t="s">
+      <c r="D1263" t="s">
         <v>244</v>
       </c>
-      <c r="E1262" t="s">
+      <c r="E1263" t="s">
         <v>25</v>
       </c>
     </row>

--- a/api/xlsx/fr/ReportingOrganisation.xlsx
+++ b/api/xlsx/fr/ReportingOrganisation.xlsx
@@ -22,12 +22,12 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:organisation-type-code</t>
+  </si>
+  <si>
     <t>codeforiati:organisation-type</t>
   </si>
   <si>
-    <t>codeforiati:organisation-type-code</t>
-  </si>
-  <si>
     <t>codeforiati:hq-country-or-region</t>
   </si>
   <si>
@@ -37,36 +37,36 @@
     <t>active</t>
   </si>
   <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>Government</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>Australia</t>
   </si>
   <si>
     <t>44000</t>
   </si>
   <si>
+    <t>40</t>
+  </si>
+  <si>
     <t>Multilateral</t>
   </si>
   <si>
-    <t>40</t>
-  </si>
-  <si>
     <t>(No country assigned)</t>
   </si>
   <si>
     <t>US-EIN-941655673</t>
   </si>
   <si>
+    <t>60</t>
+  </si>
+  <si>
     <t>Foundation</t>
   </si>
   <si>
-    <t>60</t>
-  </si>
-  <si>
     <t>United States</t>
   </si>
   <si>
@@ -76,24 +76,24 @@
     <t>GB-CHC-1038860</t>
   </si>
   <si>
+    <t>21</t>
+  </si>
+  <si>
     <t>International NGO</t>
   </si>
   <si>
-    <t>21</t>
-  </si>
-  <si>
     <t>United Kingdom</t>
   </si>
   <si>
     <t>XI-IATI-EC_DEVCO</t>
   </si>
   <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>Other Public Sector</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
     <t>SE-0</t>
   </si>
   <si>
@@ -163,12 +163,12 @@
     <t>47122</t>
   </si>
   <si>
+    <t>30</t>
+  </si>
+  <si>
     <t>Public Private Partnership</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>US-EIN-300108263</t>
   </si>
   <si>
@@ -190,12 +190,12 @@
     <t>NP-CRO-45995/063/064</t>
   </si>
   <si>
+    <t>80</t>
+  </si>
+  <si>
     <t>Academic, Training and Research</t>
   </si>
   <si>
-    <t>80</t>
-  </si>
-  <si>
     <t>Nepal</t>
   </si>
   <si>
@@ -253,12 +253,12 @@
     <t>GB-CHC-1090745</t>
   </si>
   <si>
+    <t>22</t>
+  </si>
+  <si>
     <t>National NGO</t>
   </si>
   <si>
-    <t>22</t>
-  </si>
-  <si>
     <t>GB-CHC-298316</t>
   </si>
   <si>
@@ -370,12 +370,12 @@
     <t>ZA-NPO-061-870</t>
   </si>
   <si>
+    <t>23</t>
+  </si>
+  <si>
     <t>Regional NGO</t>
   </si>
   <si>
-    <t>23</t>
-  </si>
-  <si>
     <t>South Africa</t>
   </si>
   <si>
@@ -478,10 +478,10 @@
     <t>GB-COH-03788027</t>
   </si>
   <si>
+    <t>70</t>
+  </si>
+  <si>
     <t>Private Sector</t>
-  </si>
-  <si>
-    <t>70</t>
   </si>
   <si>
     <t>GB-CHC-1058991</t>

--- a/api/xlsx/fr/ReportingOrganisation.xlsx
+++ b/api/xlsx/fr/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6340" uniqueCount="1380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6345" uniqueCount="1381">
   <si>
     <t>code</t>
   </si>
@@ -4151,6 +4151,9 @@
   </si>
   <si>
     <t>Brazil</t>
+  </si>
+  <si>
+    <t>NL-KVK-861193660</t>
   </si>
   <si>
     <t>GB-CHC-1137523</t>
@@ -4485,7 +4488,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1268"/>
+  <dimension ref="A1:E1269"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26035,12 +26038,29 @@
         <v>6</v>
       </c>
       <c r="C1268" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="D1268" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1268" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:5">
+      <c r="A1269" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B1269" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1269" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1269" t="s">
         <v>59</v>
       </c>
-      <c r="E1268" t="s">
+      <c r="E1269" t="s">
         <v>60</v>
       </c>
     </row>

--- a/api/xlsx/fr/ReportingOrganisation.xlsx
+++ b/api/xlsx/fr/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6360" uniqueCount="1384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6365" uniqueCount="1385">
   <si>
     <t>code</t>
   </si>
@@ -4097,6 +4097,9 @@
   </si>
   <si>
     <t>GB-GOR-OT1175</t>
+  </si>
+  <si>
+    <t>NG-CAC-30547</t>
   </si>
   <si>
     <t>JO-MSD-200159274</t>
@@ -4497,7 +4500,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1272"/>
+  <dimension ref="A1:E1273"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -25826,13 +25829,13 @@
         <v>6</v>
       </c>
       <c r="C1255" t="s">
-        <v>278</v>
+        <v>198</v>
       </c>
       <c r="D1255" t="s">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="E1255" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1256" spans="1:5">
@@ -25843,13 +25846,13 @@
         <v>6</v>
       </c>
       <c r="C1256" t="s">
-        <v>44</v>
+        <v>278</v>
       </c>
       <c r="D1256" t="s">
-        <v>154</v>
+        <v>79</v>
       </c>
       <c r="E1256" t="s">
-        <v>155</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1257" spans="1:5">
@@ -25860,13 +25863,13 @@
         <v>6</v>
       </c>
       <c r="C1257" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="D1257" t="s">
-        <v>59</v>
+        <v>154</v>
       </c>
       <c r="E1257" t="s">
-        <v>60</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1258" spans="1:5">
@@ -25877,7 +25880,7 @@
         <v>6</v>
       </c>
       <c r="C1258" t="s">
-        <v>244</v>
+        <v>20</v>
       </c>
       <c r="D1258" t="s">
         <v>59</v>
@@ -25894,13 +25897,13 @@
         <v>6</v>
       </c>
       <c r="C1259" t="s">
-        <v>215</v>
+        <v>244</v>
       </c>
       <c r="D1259" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="E1259" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1260" spans="1:5">
@@ -25911,7 +25914,7 @@
         <v>6</v>
       </c>
       <c r="C1260" t="s">
-        <v>1367</v>
+        <v>215</v>
       </c>
       <c r="D1260" t="s">
         <v>79</v>
@@ -25922,19 +25925,19 @@
     </row>
     <row r="1261" spans="1:5">
       <c r="A1261" t="s">
+        <v>1367</v>
+      </c>
+      <c r="B1261" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1261" t="s">
         <v>1368</v>
       </c>
-      <c r="B1261" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1261" t="s">
-        <v>20</v>
-      </c>
       <c r="D1261" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="E1261" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1262" spans="1:5">
@@ -25945,13 +25948,13 @@
         <v>6</v>
       </c>
       <c r="C1262" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D1262" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="E1262" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1263" spans="1:5">
@@ -25962,13 +25965,13 @@
         <v>6</v>
       </c>
       <c r="C1263" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D1263" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E1263" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1264" spans="1:5">
@@ -25979,13 +25982,13 @@
         <v>6</v>
       </c>
       <c r="C1264" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="D1264" t="s">
-        <v>59</v>
+        <v>21</v>
       </c>
       <c r="E1264" t="s">
-        <v>60</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1265" spans="1:5">
@@ -25996,41 +25999,41 @@
         <v>6</v>
       </c>
       <c r="C1265" t="s">
-        <v>1373</v>
+        <v>15</v>
       </c>
       <c r="D1265" t="s">
-        <v>154</v>
+        <v>59</v>
       </c>
       <c r="E1265" t="s">
-        <v>155</v>
+        <v>60</v>
       </c>
     </row>
     <row r="1266" spans="1:5">
       <c r="A1266" t="s">
+        <v>1373</v>
+      </c>
+      <c r="B1266" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1266" t="s">
         <v>1374</v>
       </c>
-      <c r="B1266" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1266" t="s">
-        <v>1375</v>
-      </c>
       <c r="D1266" t="s">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="E1266" t="s">
-        <v>80</v>
+        <v>155</v>
       </c>
     </row>
     <row r="1267" spans="1:5">
       <c r="A1267" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B1267" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1267" t="s">
         <v>1376</v>
-      </c>
-      <c r="B1267" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1267" t="s">
-        <v>1377</v>
       </c>
       <c r="D1267" t="s">
         <v>79</v>
@@ -26041,19 +26044,19 @@
     </row>
     <row r="1268" spans="1:5">
       <c r="A1268" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B1268" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1268" t="s">
         <v>1378</v>
       </c>
-      <c r="B1268" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1268" t="s">
-        <v>244</v>
-      </c>
       <c r="D1268" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="E1268" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1269" spans="1:5">
@@ -26064,13 +26067,13 @@
         <v>6</v>
       </c>
       <c r="C1269" t="s">
-        <v>20</v>
+        <v>244</v>
       </c>
       <c r="D1269" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E1269" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1270" spans="1:5">
@@ -26081,7 +26084,7 @@
         <v>6</v>
       </c>
       <c r="C1270" t="s">
-        <v>1381</v>
+        <v>20</v>
       </c>
       <c r="D1270" t="s">
         <v>21</v>
@@ -26092,19 +26095,19 @@
     </row>
     <row r="1271" spans="1:5">
       <c r="A1271" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B1271" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1271" t="s">
         <v>1382</v>
       </c>
-      <c r="B1271" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1271" t="s">
-        <v>44</v>
-      </c>
       <c r="D1271" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E1271" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1272" spans="1:5">
@@ -26115,12 +26118,29 @@
         <v>6</v>
       </c>
       <c r="C1272" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="D1272" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1272" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:5">
+      <c r="A1273" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B1273" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1273" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1273" t="s">
         <v>59</v>
       </c>
-      <c r="E1272" t="s">
+      <c r="E1273" t="s">
         <v>60</v>
       </c>
     </row>

--- a/api/xlsx/fr/ReportingOrganisation.xlsx
+++ b/api/xlsx/fr/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6375" uniqueCount="1387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6380" uniqueCount="1388">
   <si>
     <t>code</t>
   </si>
@@ -4175,6 +4175,9 @@
   </si>
   <si>
     <t>GB-CHC-1137523</t>
+  </si>
+  <si>
+    <t>US-EIN-13-4052259</t>
   </si>
 </sst>
 </file>
@@ -4506,7 +4509,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1275"/>
+  <dimension ref="A1:E1276"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26184,6 +26187,23 @@
         <v>22</v>
       </c>
     </row>
+    <row r="1276" spans="1:5">
+      <c r="A1276" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B1276" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1276" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1276" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1276" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/xlsx/fr/ReportingOrganisation.xlsx
+++ b/api/xlsx/fr/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6380" uniqueCount="1388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6385" uniqueCount="1389">
   <si>
     <t>code</t>
   </si>
@@ -4175,6 +4175,9 @@
   </si>
   <si>
     <t>GB-CHC-1137523</t>
+  </si>
+  <si>
+    <t>US-EIN-52-2135531</t>
   </si>
   <si>
     <t>US-EIN-13-4052259</t>
@@ -4509,7 +4512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1276"/>
+  <dimension ref="A1:E1277"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26204,6 +26207,23 @@
         <v>17</v>
       </c>
     </row>
+    <row r="1277" spans="1:5">
+      <c r="A1277" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B1277" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1277" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1277" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1277" t="s">
+        <v>17</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/xlsx/fr/ReportingOrganisation.xlsx
+++ b/api/xlsx/fr/ReportingOrganisation.xlsx
@@ -25,12 +25,12 @@
     <t>codeforiati:hq-country-or-region</t>
   </si>
   <si>
+    <t>codeforiati:organisation-type</t>
+  </si>
+  <si>
     <t>codeforiati:organisation-type-code</t>
   </si>
   <si>
-    <t>codeforiati:organisation-type</t>
-  </si>
-  <si>
     <t>AU-5</t>
   </si>
   <si>
@@ -40,36 +40,36 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>Government</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
-    <t>Government</t>
-  </si>
-  <si>
     <t>44000</t>
   </si>
   <si>
     <t>(No country assigned)</t>
   </si>
   <si>
+    <t>Multilateral</t>
+  </si>
+  <si>
     <t>40</t>
   </si>
   <si>
-    <t>Multilateral</t>
-  </si>
-  <si>
     <t>US-EIN-941655673</t>
   </si>
   <si>
     <t>United States</t>
   </si>
   <si>
+    <t>Foundation</t>
+  </si>
+  <si>
     <t>60</t>
   </si>
   <si>
-    <t>Foundation</t>
-  </si>
-  <si>
     <t>41AAA</t>
   </si>
   <si>
@@ -79,21 +79,21 @@
     <t>United Kingdom</t>
   </si>
   <si>
+    <t>International NGO</t>
+  </si>
+  <si>
     <t>21</t>
   </si>
   <si>
-    <t>International NGO</t>
-  </si>
-  <si>
     <t>XI-IATI-EC_DEVCO</t>
   </si>
   <si>
+    <t>Other Public Sector</t>
+  </si>
+  <si>
     <t>15</t>
   </si>
   <si>
-    <t>Other Public Sector</t>
-  </si>
-  <si>
     <t>SE-0</t>
   </si>
   <si>
@@ -163,12 +163,12 @@
     <t>47122</t>
   </si>
   <si>
+    <t>Public Private Partnership</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
-    <t>Public Private Partnership</t>
-  </si>
-  <si>
     <t>US-EIN-300108263</t>
   </si>
   <si>
@@ -193,12 +193,12 @@
     <t>Nepal</t>
   </si>
   <si>
+    <t>Academic, Training and Research</t>
+  </si>
+  <si>
     <t>80</t>
   </si>
   <si>
-    <t>Academic, Training and Research</t>
-  </si>
-  <si>
     <t>GB-CHC-327421</t>
   </si>
   <si>
@@ -253,12 +253,12 @@
     <t>GB-CHC-1090745</t>
   </si>
   <si>
+    <t>National NGO</t>
+  </si>
+  <si>
     <t>22</t>
   </si>
   <si>
-    <t>National NGO</t>
-  </si>
-  <si>
     <t>GB-CHC-298316</t>
   </si>
   <si>
@@ -373,12 +373,12 @@
     <t>South Africa</t>
   </si>
   <si>
+    <t>Regional NGO</t>
+  </si>
+  <si>
     <t>23</t>
   </si>
   <si>
-    <t>Regional NGO</t>
-  </si>
-  <si>
     <t>CH-FDJP-CHE-110347351</t>
   </si>
   <si>
@@ -481,10 +481,10 @@
     <t>GB-COH-03788027</t>
   </si>
   <si>
+    <t>Private Sector</t>
+  </si>
+  <si>
     <t>70</t>
-  </si>
-  <si>
-    <t>Private Sector</t>
   </si>
   <si>
     <t>GB-CHC-1058991</t>

--- a/api/xlsx/fr/ReportingOrganisation.xlsx
+++ b/api/xlsx/fr/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6385" uniqueCount="1389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6390" uniqueCount="1390">
   <si>
     <t>code</t>
   </si>
@@ -4178,6 +4178,9 @@
   </si>
   <si>
     <t>US-EIN-52-2135531</t>
+  </si>
+  <si>
+    <t>GB-COH-02515034</t>
   </si>
   <si>
     <t>US-EIN-13-4052259</t>
@@ -4512,7 +4515,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E1277"/>
+  <dimension ref="A1:E1278"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
@@ -26215,12 +26218,29 @@
         <v>6</v>
       </c>
       <c r="C1277" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1277" t="s">
+        <v>155</v>
+      </c>
+      <c r="E1277" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:5">
+      <c r="A1278" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B1278" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1278" t="s">
         <v>15</v>
       </c>
-      <c r="D1277" t="s">
-        <v>21</v>
-      </c>
-      <c r="E1277" t="s">
+      <c r="D1278" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1278" t="s">
         <v>22</v>
       </c>
     </row>

--- a/api/xlsx/fr/ReportingOrganisation.xlsx
+++ b/api/xlsx/fr/ReportingOrganisation.xlsx
@@ -22,66 +22,66 @@
     <t>status</t>
   </si>
   <si>
+    <t>codeforiati:organisation-type</t>
+  </si>
+  <si>
+    <t>codeforiati:hq-country-or-region</t>
+  </si>
+  <si>
+    <t>codeforiati:registry-identifier</t>
+  </si>
+  <si>
     <t>codeforiati:organisation-type-code</t>
   </si>
   <si>
-    <t>codeforiati:hq-country-or-region</t>
-  </si>
-  <si>
-    <t>codeforiati:registry-identifier</t>
-  </si>
-  <si>
-    <t>codeforiati:organisation-type</t>
-  </si>
-  <si>
     <t>AU-5</t>
   </si>
   <si>
     <t>active</t>
   </si>
   <si>
+    <t>Government</t>
+  </si>
+  <si>
+    <t>Australia</t>
+  </si>
+  <si>
+    <t>ausgov</t>
+  </si>
+  <si>
     <t>10</t>
   </si>
   <si>
-    <t>Australia</t>
-  </si>
-  <si>
-    <t>ausgov</t>
-  </si>
-  <si>
-    <t>Government</t>
-  </si>
-  <si>
     <t>44000</t>
   </si>
   <si>
+    <t>Multilateral</t>
+  </si>
+  <si>
+    <t>(No country assigned)</t>
+  </si>
+  <si>
+    <t>worldbank</t>
+  </si>
+  <si>
     <t>40</t>
   </si>
   <si>
-    <t>(No country assigned)</t>
-  </si>
-  <si>
-    <t>worldbank</t>
-  </si>
-  <si>
-    <t>Multilateral</t>
-  </si>
-  <si>
     <t>US-EIN-941655673</t>
   </si>
   <si>
+    <t>Foundation</t>
+  </si>
+  <si>
+    <t>United States</t>
+  </si>
+  <si>
+    <t>hewlett-foundation</t>
+  </si>
+  <si>
     <t>60</t>
   </si>
   <si>
-    <t>United States</t>
-  </si>
-  <si>
-    <t>hewlett-foundation</t>
-  </si>
-  <si>
-    <t>Foundation</t>
-  </si>
-  <si>
     <t>41AAA</t>
   </si>
   <si>
@@ -91,30 +91,30 @@
     <t>GB-CHC-1038860</t>
   </si>
   <si>
+    <t>International NGO</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>f-aids</t>
+  </si>
+  <si>
     <t>21</t>
   </si>
   <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>f-aids</t>
-  </si>
-  <si>
-    <t>International NGO</t>
-  </si>
-  <si>
     <t>XI-IATI-EC_DEVCO</t>
   </si>
   <si>
+    <t>Other Public Sector</t>
+  </si>
+  <si>
+    <t>ec-devco</t>
+  </si>
+  <si>
     <t>15</t>
   </si>
   <si>
-    <t>ec-devco</t>
-  </si>
-  <si>
-    <t>Other Public Sector</t>
-  </si>
-  <si>
     <t>SE-0</t>
   </si>
   <si>
@@ -226,15 +226,15 @@
     <t>47122</t>
   </si>
   <si>
+    <t>Public Private Partnership</t>
+  </si>
+  <si>
+    <t>gavi</t>
+  </si>
+  <si>
     <t>30</t>
   </si>
   <si>
-    <t>gavi</t>
-  </si>
-  <si>
-    <t>Public Private Partnership</t>
-  </si>
-  <si>
     <t>US-EIN-300108263</t>
   </si>
   <si>
@@ -274,18 +274,18 @@
     <t>NP-CRO-45995/063/064</t>
   </si>
   <si>
+    <t>Academic, Training and Research</t>
+  </si>
+  <si>
+    <t>Nepal</t>
+  </si>
+  <si>
+    <t>yipl</t>
+  </si>
+  <si>
     <t>80</t>
   </si>
   <si>
-    <t>Nepal</t>
-  </si>
-  <si>
-    <t>yipl</t>
-  </si>
-  <si>
-    <t>Academic, Training and Research</t>
-  </si>
-  <si>
     <t>GB-CHC-327421</t>
   </si>
   <si>
@@ -388,15 +388,15 @@
     <t>GB-CHC-1090745</t>
   </si>
   <si>
+    <t>National NGO</t>
+  </si>
+  <si>
+    <t>icauk</t>
+  </si>
+  <si>
     <t>22</t>
   </si>
   <si>
-    <t>icauk</t>
-  </si>
-  <si>
-    <t>National NGO</t>
-  </si>
-  <si>
     <t>GB-CHC-298316</t>
   </si>
   <si>
@@ -616,18 +616,18 @@
     <t>ZA-NPO-061-870</t>
   </si>
   <si>
+    <t>Regional NGO</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
+    <t>sacbc</t>
+  </si>
+  <si>
     <t>23</t>
   </si>
   <si>
-    <t>South Africa</t>
-  </si>
-  <si>
-    <t>sacbc</t>
-  </si>
-  <si>
-    <t>Regional NGO</t>
-  </si>
-  <si>
     <t>CH-FDJP-CHE-110347351</t>
   </si>
   <si>
@@ -820,13 +820,13 @@
     <t>GB-COH-03788027</t>
   </si>
   <si>
+    <t>Private Sector</t>
+  </si>
+  <si>
+    <t>tripleline_crownagents</t>
+  </si>
+  <si>
     <t>70</t>
-  </si>
-  <si>
-    <t>tripleline_crownagents</t>
-  </si>
-  <si>
-    <t>Private Sector</t>
   </si>
   <si>
     <t>GB-CHC-1058991</t>

--- a/api/xlsx/fr/ReportingOrganisation.xlsx
+++ b/api/xlsx/fr/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7714" uniqueCount="2680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7720" uniqueCount="2682">
   <si>
     <t>code</t>
   </si>
@@ -8054,6 +8054,12 @@
   </si>
   <si>
     <t>mdif</t>
+  </si>
+  <si>
+    <t>BE-BCE_KBO-0464147473</t>
+  </si>
+  <si>
+    <t>lhac</t>
   </si>
 </sst>
 </file>
@@ -8385,7 +8391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F1286"/>
+  <dimension ref="A1:F1287"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -34102,6 +34108,26 @@
         <v>21</v>
       </c>
     </row>
+    <row r="1287" spans="1:6">
+      <c r="A1287" t="s">
+        <v>2680</v>
+      </c>
+      <c r="B1287" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1287" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1287" t="s">
+        <v>2681</v>
+      </c>
+      <c r="E1287" t="s">
+        <v>130</v>
+      </c>
+      <c r="F1287" t="s">
+        <v>335</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/api/xlsx/fr/ReportingOrganisation.xlsx
+++ b/api/xlsx/fr/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13968" uniqueCount="5697">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14058" uniqueCount="5729">
   <si>
     <t>code</t>
   </si>
@@ -16702,6 +16702,18 @@
     <t>arin</t>
   </si>
   <si>
+    <t>IN-MHA-231660448</t>
+  </si>
+  <si>
+    <t>ccdc_india</t>
+  </si>
+  <si>
+    <t>TG-NIF-1000047187</t>
+  </si>
+  <si>
+    <t>wildafao</t>
+  </si>
+  <si>
     <t>CH-FDJP-CHE365512867</t>
   </si>
   <si>
@@ -16726,6 +16738,60 @@
     <t>adra-sweden</t>
   </si>
   <si>
+    <t>GB-COH-07921860</t>
+  </si>
+  <si>
+    <t>iigcc</t>
+  </si>
+  <si>
+    <t>MZ-MOJ-100493543</t>
+  </si>
+  <si>
+    <t>apite</t>
+  </si>
+  <si>
+    <t>GB-COH-12075030</t>
+  </si>
+  <si>
+    <t>Private Sector in Provider Country</t>
+  </si>
+  <si>
+    <t>71</t>
+  </si>
+  <si>
+    <t>ica</t>
+  </si>
+  <si>
+    <t>GB-CHC-1111719</t>
+  </si>
+  <si>
+    <t>aaf</t>
+  </si>
+  <si>
+    <t>TZ-NNCB-00NGO00009862</t>
+  </si>
+  <si>
+    <t>mviwanya</t>
+  </si>
+  <si>
+    <t>UA-EDR-45583070</t>
+  </si>
+  <si>
+    <t>vruna</t>
+  </si>
+  <si>
+    <t>XI-ROR-01ej9dk98</t>
+  </si>
+  <si>
+    <t>unimelb</t>
+  </si>
+  <si>
+    <t>TH-MOI-KhorThor3005</t>
+  </si>
+  <si>
+    <t>tlhr</t>
+  </si>
+  <si>
     <t>SE-ON-252002-6135</t>
   </si>
   <si>
@@ -16766,6 +16832,36 @@
   </si>
   <si>
     <t>pangeaafrica</t>
+  </si>
+  <si>
+    <t>ZA-CIP-2025-956558-08</t>
+  </si>
+  <si>
+    <t>iff-npc</t>
+  </si>
+  <si>
+    <t>ZA-CIT-9063151162</t>
+  </si>
+  <si>
+    <t>ukzn</t>
+  </si>
+  <si>
+    <t>MZ-MOJ-821-B</t>
+  </si>
+  <si>
+    <t>asa</t>
+  </si>
+  <si>
+    <t>BR-CNPJ-01567601-0001-43</t>
+  </si>
+  <si>
+    <t>ufg</t>
+  </si>
+  <si>
+    <t>ET-CSA-0067</t>
+  </si>
+  <si>
+    <t>tsda</t>
   </si>
   <si>
     <t>CR-RPJ-3-002-248583</t>
@@ -17436,7 +17532,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2111"/>
+  <dimension ref="A1:G2126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -62272,16 +62368,16 @@
         <v>9</v>
       </c>
       <c r="D2045" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2045" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2045" t="s">
         <v>5563</v>
       </c>
       <c r="G2045" t="s">
-        <v>72</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2046" spans="1:7">
@@ -62292,16 +62388,16 @@
         <v>9</v>
       </c>
       <c r="D2046" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="E2046" t="s">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="F2046" t="s">
         <v>5565</v>
       </c>
       <c r="G2046" t="s">
-        <v>437</v>
+        <v>4544</v>
       </c>
     </row>
     <row r="2047" spans="1:7">
@@ -62312,16 +62408,16 @@
         <v>9</v>
       </c>
       <c r="D2047" t="s">
-        <v>175</v>
+        <v>31</v>
       </c>
       <c r="E2047" t="s">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="F2047" t="s">
         <v>5567</v>
       </c>
       <c r="G2047" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2048" spans="1:7">
@@ -62332,16 +62428,16 @@
         <v>9</v>
       </c>
       <c r="D2048" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="E2048" t="s">
-        <v>32</v>
+        <v>11</v>
       </c>
       <c r="F2048" t="s">
         <v>5569</v>
       </c>
       <c r="G2048" t="s">
-        <v>47</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2049" spans="1:7">
@@ -62352,10 +62448,10 @@
         <v>9</v>
       </c>
       <c r="D2049" t="s">
-        <v>4878</v>
+        <v>175</v>
       </c>
       <c r="E2049" t="s">
-        <v>4879</v>
+        <v>176</v>
       </c>
       <c r="F2049" t="s">
         <v>5571</v>
@@ -62392,10 +62488,10 @@
         <v>9</v>
       </c>
       <c r="D2051" t="s">
-        <v>370</v>
+        <v>37</v>
       </c>
       <c r="E2051" t="s">
-        <v>371</v>
+        <v>38</v>
       </c>
       <c r="F2051" t="s">
         <v>5575</v>
@@ -62412,16 +62508,16 @@
         <v>9</v>
       </c>
       <c r="D2052" t="s">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="E2052" t="s">
-        <v>11</v>
+        <v>176</v>
       </c>
       <c r="F2052" t="s">
         <v>5577</v>
       </c>
       <c r="G2052" t="s">
-        <v>47</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="2053" spans="1:7">
@@ -62432,61 +62528,61 @@
         <v>9</v>
       </c>
       <c r="D2053" t="s">
-        <v>370</v>
+        <v>5579</v>
       </c>
       <c r="E2053" t="s">
-        <v>371</v>
+        <v>5580</v>
       </c>
       <c r="F2053" t="s">
-        <v>5579</v>
+        <v>5581</v>
       </c>
       <c r="G2053" t="s">
-        <v>2388</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2054" spans="1:7">
       <c r="A2054" t="s">
-        <v>5580</v>
+        <v>5582</v>
       </c>
       <c r="C2054" t="s">
         <v>9</v>
       </c>
       <c r="D2054" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E2054" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F2054" t="s">
-        <v>5581</v>
+        <v>5583</v>
       </c>
       <c r="G2054" t="s">
-        <v>461</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2055" spans="1:7">
       <c r="A2055" t="s">
-        <v>5582</v>
+        <v>5584</v>
       </c>
       <c r="C2055" t="s">
         <v>9</v>
       </c>
       <c r="D2055" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="E2055" t="s">
-        <v>121</v>
+        <v>176</v>
       </c>
       <c r="F2055" t="s">
-        <v>5583</v>
+        <v>5585</v>
       </c>
       <c r="G2055" t="s">
-        <v>706</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2056" spans="1:7">
       <c r="A2056" t="s">
-        <v>5584</v>
+        <v>5586</v>
       </c>
       <c r="C2056" t="s">
         <v>9</v>
@@ -62498,81 +62594,87 @@
         <v>176</v>
       </c>
       <c r="F2056" t="s">
-        <v>5585</v>
+        <v>5587</v>
       </c>
       <c r="G2056" t="s">
-        <v>2872</v>
+        <v>926</v>
       </c>
     </row>
     <row r="2057" spans="1:7">
       <c r="A2057" t="s">
-        <v>5586</v>
+        <v>5588</v>
       </c>
       <c r="C2057" t="s">
         <v>9</v>
       </c>
+      <c r="D2057" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2057" t="s">
+        <v>371</v>
+      </c>
       <c r="F2057" t="s">
-        <v>5587</v>
+        <v>5589</v>
       </c>
       <c r="G2057" t="s">
-        <v>358</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2058" spans="1:7">
       <c r="A2058" t="s">
-        <v>5588</v>
+        <v>5590</v>
       </c>
       <c r="C2058" t="s">
         <v>9</v>
       </c>
       <c r="D2058" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="E2058" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="F2058" t="s">
-        <v>5589</v>
+        <v>5591</v>
       </c>
       <c r="G2058" t="s">
-        <v>634</v>
+        <v>4438</v>
       </c>
     </row>
     <row r="2059" spans="1:7">
       <c r="A2059" t="s">
-        <v>5590</v>
+        <v>5592</v>
       </c>
       <c r="C2059" t="s">
         <v>9</v>
       </c>
       <c r="D2059" t="s">
-        <v>16</v>
+        <v>4878</v>
       </c>
       <c r="E2059" t="s">
-        <v>17</v>
+        <v>4879</v>
       </c>
       <c r="F2059" t="s">
-        <v>5591</v>
+        <v>5593</v>
       </c>
       <c r="G2059" t="s">
-        <v>634</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2060" spans="1:7">
       <c r="A2060" t="s">
-        <v>5592</v>
+        <v>5594</v>
       </c>
       <c r="C2060" t="s">
         <v>9</v>
       </c>
       <c r="D2060" t="s">
-        <v>175</v>
+        <v>31</v>
       </c>
       <c r="E2060" t="s">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="F2060" t="s">
-        <v>5593</v>
+        <v>5595</v>
       </c>
       <c r="G2060" t="s">
         <v>47</v>
@@ -62580,39 +62682,39 @@
     </row>
     <row r="2061" spans="1:7">
       <c r="A2061" t="s">
-        <v>5594</v>
+        <v>5596</v>
       </c>
       <c r="C2061" t="s">
         <v>9</v>
       </c>
       <c r="D2061" t="s">
-        <v>5428</v>
+        <v>370</v>
       </c>
       <c r="E2061" t="s">
-        <v>5429</v>
+        <v>371</v>
       </c>
       <c r="F2061" t="s">
-        <v>5595</v>
+        <v>5597</v>
       </c>
       <c r="G2061" t="s">
-        <v>437</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2062" spans="1:7">
       <c r="A2062" t="s">
-        <v>5596</v>
+        <v>5598</v>
       </c>
       <c r="C2062" t="s">
         <v>9</v>
       </c>
       <c r="D2062" t="s">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="E2062" t="s">
-        <v>176</v>
+        <v>11</v>
       </c>
       <c r="F2062" t="s">
-        <v>5597</v>
+        <v>5599</v>
       </c>
       <c r="G2062" t="s">
         <v>47</v>
@@ -62620,135 +62722,147 @@
     </row>
     <row r="2063" spans="1:7">
       <c r="A2063" t="s">
-        <v>5598</v>
+        <v>5600</v>
       </c>
       <c r="C2063" t="s">
         <v>9</v>
       </c>
+      <c r="D2063" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2063" t="s">
+        <v>371</v>
+      </c>
       <c r="F2063" t="s">
-        <v>5599</v>
+        <v>5601</v>
       </c>
       <c r="G2063" t="s">
-        <v>47</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="2064" spans="1:7">
       <c r="A2064" t="s">
-        <v>5600</v>
+        <v>5602</v>
       </c>
       <c r="C2064" t="s">
         <v>9</v>
       </c>
       <c r="D2064" t="s">
-        <v>120</v>
+        <v>31</v>
       </c>
       <c r="E2064" t="s">
-        <v>121</v>
+        <v>32</v>
       </c>
       <c r="F2064" t="s">
-        <v>5601</v>
+        <v>5603</v>
       </c>
       <c r="G2064" t="s">
-        <v>4438</v>
+        <v>461</v>
       </c>
     </row>
     <row r="2065" spans="1:7">
       <c r="A2065" t="s">
-        <v>5602</v>
+        <v>5604</v>
       </c>
       <c r="C2065" t="s">
         <v>9</v>
       </c>
       <c r="D2065" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="E2065" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="F2065" t="s">
-        <v>5603</v>
+        <v>5605</v>
       </c>
       <c r="G2065" t="s">
-        <v>403</v>
+        <v>706</v>
       </c>
     </row>
     <row r="2066" spans="1:7">
       <c r="A2066" t="s">
-        <v>5604</v>
+        <v>5606</v>
       </c>
       <c r="C2066" t="s">
         <v>9</v>
       </c>
       <c r="D2066" t="s">
-        <v>22</v>
+        <v>4878</v>
       </c>
       <c r="E2066" t="s">
-        <v>23</v>
+        <v>4879</v>
       </c>
       <c r="F2066" t="s">
-        <v>5605</v>
+        <v>5607</v>
       </c>
       <c r="G2066" t="s">
-        <v>47</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2067" spans="1:7">
       <c r="A2067" t="s">
-        <v>5606</v>
+        <v>5608</v>
       </c>
       <c r="C2067" t="s">
         <v>9</v>
       </c>
       <c r="D2067" t="s">
-        <v>31</v>
+        <v>370</v>
       </c>
       <c r="E2067" t="s">
-        <v>32</v>
+        <v>371</v>
       </c>
       <c r="F2067" t="s">
-        <v>5607</v>
+        <v>5609</v>
       </c>
       <c r="G2067" t="s">
-        <v>482</v>
+        <v>293</v>
       </c>
     </row>
     <row r="2068" spans="1:7">
       <c r="A2068" t="s">
-        <v>5608</v>
+        <v>5610</v>
       </c>
       <c r="C2068" t="s">
         <v>9</v>
       </c>
       <c r="D2068" t="s">
-        <v>4878</v>
+        <v>5428</v>
       </c>
       <c r="E2068" t="s">
-        <v>4879</v>
+        <v>5429</v>
       </c>
       <c r="F2068" t="s">
-        <v>5609</v>
+        <v>5611</v>
       </c>
       <c r="G2068" t="s">
-        <v>5610</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="2069" spans="1:7">
       <c r="A2069" t="s">
-        <v>5611</v>
+        <v>5612</v>
       </c>
       <c r="C2069" t="s">
         <v>9</v>
       </c>
+      <c r="D2069" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2069" t="s">
+        <v>371</v>
+      </c>
       <c r="F2069" t="s">
-        <v>5612</v>
+        <v>5613</v>
       </c>
       <c r="G2069" t="s">
-        <v>47</v>
+        <v>4266</v>
       </c>
     </row>
     <row r="2070" spans="1:7">
       <c r="A2070" t="s">
-        <v>5613</v>
+        <v>5614</v>
       </c>
       <c r="C2070" t="s">
         <v>9</v>
@@ -62760,107 +62874,101 @@
         <v>176</v>
       </c>
       <c r="F2070" t="s">
-        <v>5614</v>
+        <v>5615</v>
       </c>
       <c r="G2070" t="s">
-        <v>684</v>
+        <v>1689</v>
       </c>
     </row>
     <row r="2071" spans="1:7">
       <c r="A2071" t="s">
-        <v>5615</v>
+        <v>5616</v>
       </c>
       <c r="C2071" t="s">
         <v>9</v>
       </c>
       <c r="D2071" t="s">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="E2071" t="s">
-        <v>11</v>
+        <v>176</v>
       </c>
       <c r="F2071" t="s">
-        <v>5616</v>
+        <v>5617</v>
       </c>
       <c r="G2071" t="s">
-        <v>504</v>
+        <v>2872</v>
       </c>
     </row>
     <row r="2072" spans="1:7">
       <c r="A2072" t="s">
-        <v>5617</v>
+        <v>5618</v>
       </c>
       <c r="C2072" t="s">
         <v>9</v>
       </c>
-      <c r="D2072" t="s">
-        <v>175</v>
-      </c>
-      <c r="E2072" t="s">
-        <v>176</v>
-      </c>
       <c r="F2072" t="s">
-        <v>5618</v>
+        <v>5619</v>
       </c>
       <c r="G2072" t="s">
-        <v>600</v>
+        <v>358</v>
       </c>
     </row>
     <row r="2073" spans="1:7">
       <c r="A2073" t="s">
-        <v>5619</v>
+        <v>5620</v>
       </c>
       <c r="C2073" t="s">
         <v>9</v>
       </c>
       <c r="D2073" t="s">
-        <v>175</v>
+        <v>31</v>
       </c>
       <c r="E2073" t="s">
-        <v>176</v>
+        <v>32</v>
       </c>
       <c r="F2073" t="s">
-        <v>5620</v>
+        <v>5621</v>
       </c>
       <c r="G2073" t="s">
-        <v>437</v>
+        <v>634</v>
       </c>
     </row>
     <row r="2074" spans="1:7">
       <c r="A2074" t="s">
-        <v>5621</v>
+        <v>5622</v>
       </c>
       <c r="C2074" t="s">
         <v>9</v>
       </c>
       <c r="D2074" t="s">
-        <v>120</v>
+        <v>16</v>
       </c>
       <c r="E2074" t="s">
-        <v>121</v>
+        <v>17</v>
       </c>
       <c r="F2074" t="s">
-        <v>5622</v>
+        <v>5623</v>
       </c>
       <c r="G2074" t="s">
-        <v>87</v>
+        <v>634</v>
       </c>
     </row>
     <row r="2075" spans="1:7">
       <c r="A2075" t="s">
-        <v>5623</v>
+        <v>5624</v>
       </c>
       <c r="C2075" t="s">
         <v>9</v>
       </c>
       <c r="D2075" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2075" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2075" t="s">
-        <v>5624</v>
+        <v>5625</v>
       </c>
       <c r="G2075" t="s">
         <v>47</v>
@@ -62868,27 +62976,27 @@
     </row>
     <row r="2076" spans="1:7">
       <c r="A2076" t="s">
-        <v>5625</v>
+        <v>5626</v>
       </c>
       <c r="C2076" t="s">
         <v>9</v>
       </c>
       <c r="D2076" t="s">
-        <v>22</v>
+        <v>5428</v>
       </c>
       <c r="E2076" t="s">
-        <v>23</v>
+        <v>5429</v>
       </c>
       <c r="F2076" t="s">
-        <v>5626</v>
+        <v>5627</v>
       </c>
       <c r="G2076" t="s">
-        <v>47</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2077" spans="1:7">
       <c r="A2077" t="s">
-        <v>5627</v>
+        <v>5628</v>
       </c>
       <c r="C2077" t="s">
         <v>9</v>
@@ -62900,135 +63008,135 @@
         <v>176</v>
       </c>
       <c r="F2077" t="s">
-        <v>5628</v>
+        <v>5629</v>
       </c>
       <c r="G2077" t="s">
-        <v>2001</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2078" spans="1:7">
       <c r="A2078" t="s">
-        <v>5629</v>
+        <v>5630</v>
       </c>
       <c r="C2078" t="s">
         <v>9</v>
       </c>
-      <c r="D2078" t="s">
-        <v>370</v>
-      </c>
-      <c r="E2078" t="s">
-        <v>371</v>
-      </c>
       <c r="F2078" t="s">
-        <v>5630</v>
+        <v>5631</v>
       </c>
       <c r="G2078" t="s">
-        <v>600</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2079" spans="1:7">
       <c r="A2079" t="s">
-        <v>5631</v>
+        <v>5632</v>
       </c>
       <c r="C2079" t="s">
         <v>9</v>
       </c>
       <c r="D2079" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="E2079" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="F2079" t="s">
-        <v>5632</v>
+        <v>5633</v>
       </c>
       <c r="G2079" t="s">
-        <v>1927</v>
+        <v>4438</v>
       </c>
     </row>
     <row r="2080" spans="1:7">
       <c r="A2080" t="s">
-        <v>5633</v>
+        <v>5634</v>
       </c>
       <c r="C2080" t="s">
         <v>9</v>
       </c>
+      <c r="D2080" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2080" t="s">
+        <v>176</v>
+      </c>
       <c r="F2080" t="s">
-        <v>5634</v>
+        <v>5635</v>
       </c>
       <c r="G2080" t="s">
-        <v>706</v>
+        <v>403</v>
       </c>
     </row>
     <row r="2081" spans="1:7">
       <c r="A2081" t="s">
-        <v>5635</v>
+        <v>5636</v>
       </c>
       <c r="C2081" t="s">
         <v>9</v>
       </c>
       <c r="D2081" t="s">
-        <v>370</v>
+        <v>22</v>
       </c>
       <c r="E2081" t="s">
-        <v>371</v>
+        <v>23</v>
       </c>
       <c r="F2081" t="s">
-        <v>5636</v>
+        <v>5637</v>
       </c>
       <c r="G2081" t="s">
-        <v>471</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2082" spans="1:7">
       <c r="A2082" t="s">
-        <v>5637</v>
+        <v>5638</v>
       </c>
       <c r="C2082" t="s">
         <v>9</v>
       </c>
       <c r="D2082" t="s">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="E2082" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F2082" t="s">
-        <v>5638</v>
+        <v>5639</v>
       </c>
       <c r="G2082" t="s">
-        <v>34</v>
+        <v>482</v>
       </c>
     </row>
     <row r="2083" spans="1:7">
       <c r="A2083" t="s">
-        <v>5639</v>
+        <v>5640</v>
       </c>
       <c r="C2083" t="s">
         <v>9</v>
       </c>
       <c r="D2083" t="s">
-        <v>370</v>
+        <v>4878</v>
       </c>
       <c r="E2083" t="s">
-        <v>371</v>
+        <v>4879</v>
       </c>
       <c r="F2083" t="s">
-        <v>5640</v>
+        <v>5641</v>
       </c>
       <c r="G2083" t="s">
-        <v>34</v>
+        <v>5642</v>
       </c>
     </row>
     <row r="2084" spans="1:7">
       <c r="A2084" t="s">
-        <v>5641</v>
+        <v>5643</v>
       </c>
       <c r="C2084" t="s">
         <v>9</v>
       </c>
       <c r="F2084" t="s">
-        <v>5642</v>
+        <v>5644</v>
       </c>
       <c r="G2084" t="s">
         <v>47</v>
@@ -63036,7 +63144,7 @@
     </row>
     <row r="2085" spans="1:7">
       <c r="A2085" t="s">
-        <v>5643</v>
+        <v>5645</v>
       </c>
       <c r="C2085" t="s">
         <v>9</v>
@@ -63048,35 +63156,35 @@
         <v>176</v>
       </c>
       <c r="F2085" t="s">
-        <v>5644</v>
+        <v>5646</v>
       </c>
       <c r="G2085" t="s">
-        <v>2498</v>
+        <v>684</v>
       </c>
     </row>
     <row r="2086" spans="1:7">
       <c r="A2086" t="s">
-        <v>5645</v>
+        <v>5647</v>
       </c>
       <c r="C2086" t="s">
         <v>9</v>
       </c>
       <c r="D2086" t="s">
-        <v>175</v>
+        <v>10</v>
       </c>
       <c r="E2086" t="s">
-        <v>176</v>
+        <v>11</v>
       </c>
       <c r="F2086" t="s">
-        <v>5646</v>
+        <v>5648</v>
       </c>
       <c r="G2086" t="s">
-        <v>47</v>
+        <v>504</v>
       </c>
     </row>
     <row r="2087" spans="1:7">
       <c r="A2087" t="s">
-        <v>5647</v>
+        <v>5649</v>
       </c>
       <c r="C2087" t="s">
         <v>9</v>
@@ -63088,129 +63196,135 @@
         <v>176</v>
       </c>
       <c r="F2087" t="s">
-        <v>5648</v>
+        <v>5650</v>
       </c>
       <c r="G2087" t="s">
-        <v>47</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2088" spans="1:7">
       <c r="A2088" t="s">
-        <v>5649</v>
+        <v>5651</v>
       </c>
       <c r="C2088" t="s">
         <v>9</v>
       </c>
       <c r="D2088" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2088" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2088" t="s">
-        <v>5650</v>
+        <v>5652</v>
       </c>
       <c r="G2088" t="s">
-        <v>47</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2089" spans="1:7">
       <c r="A2089" t="s">
-        <v>5651</v>
+        <v>5653</v>
       </c>
       <c r="C2089" t="s">
         <v>9</v>
       </c>
       <c r="D2089" t="s">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="E2089" t="s">
-        <v>176</v>
+        <v>121</v>
       </c>
       <c r="F2089" t="s">
-        <v>5652</v>
+        <v>5654</v>
       </c>
       <c r="G2089" t="s">
-        <v>926</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2090" spans="1:7">
       <c r="A2090" t="s">
-        <v>5653</v>
+        <v>5655</v>
       </c>
       <c r="C2090" t="s">
         <v>9</v>
       </c>
+      <c r="D2090" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2090" t="s">
+        <v>32</v>
+      </c>
       <c r="F2090" t="s">
-        <v>5654</v>
+        <v>5656</v>
       </c>
       <c r="G2090" t="s">
-        <v>437</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2091" spans="1:7">
       <c r="A2091" t="s">
-        <v>5655</v>
+        <v>5657</v>
       </c>
       <c r="C2091" t="s">
         <v>9</v>
       </c>
       <c r="D2091" t="s">
-        <v>370</v>
+        <v>22</v>
       </c>
       <c r="E2091" t="s">
-        <v>371</v>
+        <v>23</v>
       </c>
       <c r="F2091" t="s">
-        <v>5656</v>
+        <v>5658</v>
       </c>
       <c r="G2091" t="s">
-        <v>3610</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2092" spans="1:7">
       <c r="A2092" t="s">
-        <v>5657</v>
+        <v>5659</v>
       </c>
       <c r="C2092" t="s">
         <v>9</v>
       </c>
       <c r="D2092" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2092" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2092" t="s">
-        <v>5658</v>
+        <v>5660</v>
       </c>
       <c r="G2092" t="s">
-        <v>25</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="2093" spans="1:7">
       <c r="A2093" t="s">
-        <v>5659</v>
+        <v>5661</v>
       </c>
       <c r="C2093" t="s">
         <v>9</v>
       </c>
       <c r="D2093" t="s">
-        <v>175</v>
+        <v>370</v>
       </c>
       <c r="E2093" t="s">
-        <v>176</v>
+        <v>371</v>
       </c>
       <c r="F2093" t="s">
-        <v>5660</v>
+        <v>5662</v>
       </c>
       <c r="G2093" t="s">
-        <v>1911</v>
+        <v>600</v>
       </c>
     </row>
     <row r="2094" spans="1:7">
       <c r="A2094" t="s">
-        <v>5661</v>
+        <v>5663</v>
       </c>
       <c r="C2094" t="s">
         <v>9</v>
@@ -63222,121 +63336,115 @@
         <v>176</v>
       </c>
       <c r="F2094" t="s">
-        <v>5662</v>
+        <v>5664</v>
       </c>
       <c r="G2094" t="s">
-        <v>5610</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="2095" spans="1:7">
       <c r="A2095" t="s">
-        <v>5663</v>
+        <v>5665</v>
       </c>
       <c r="C2095" t="s">
         <v>9</v>
       </c>
-      <c r="D2095" t="s">
-        <v>175</v>
-      </c>
-      <c r="E2095" t="s">
-        <v>176</v>
-      </c>
       <c r="F2095" t="s">
-        <v>5664</v>
+        <v>5666</v>
       </c>
       <c r="G2095" t="s">
-        <v>5549</v>
+        <v>706</v>
       </c>
     </row>
     <row r="2096" spans="1:7">
       <c r="A2096" t="s">
-        <v>5665</v>
+        <v>5667</v>
       </c>
       <c r="C2096" t="s">
         <v>9</v>
       </c>
+      <c r="D2096" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2096" t="s">
+        <v>371</v>
+      </c>
       <c r="F2096" t="s">
-        <v>5666</v>
+        <v>5668</v>
       </c>
       <c r="G2096" t="s">
-        <v>47</v>
+        <v>471</v>
       </c>
     </row>
     <row r="2097" spans="1:7">
       <c r="A2097" t="s">
-        <v>5667</v>
+        <v>5669</v>
       </c>
       <c r="C2097" t="s">
         <v>9</v>
       </c>
       <c r="D2097" t="s">
-        <v>120</v>
+        <v>22</v>
       </c>
       <c r="E2097" t="s">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="F2097" t="s">
-        <v>5668</v>
+        <v>5670</v>
       </c>
       <c r="G2097" t="s">
-        <v>358</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2098" spans="1:7">
       <c r="A2098" t="s">
-        <v>5669</v>
+        <v>5671</v>
       </c>
       <c r="C2098" t="s">
         <v>9</v>
       </c>
       <c r="D2098" t="s">
-        <v>175</v>
+        <v>370</v>
       </c>
       <c r="E2098" t="s">
-        <v>176</v>
+        <v>371</v>
       </c>
       <c r="F2098" t="s">
-        <v>5670</v>
+        <v>5672</v>
       </c>
       <c r="G2098" t="s">
-        <v>926</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2099" spans="1:7">
       <c r="A2099" t="s">
-        <v>5671</v>
+        <v>5673</v>
       </c>
       <c r="C2099" t="s">
         <v>9</v>
       </c>
-      <c r="D2099" t="s">
-        <v>370</v>
-      </c>
-      <c r="E2099" t="s">
-        <v>371</v>
-      </c>
       <c r="F2099" t="s">
-        <v>5672</v>
+        <v>5674</v>
       </c>
       <c r="G2099" t="s">
-        <v>1689</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2100" spans="1:7">
       <c r="A2100" t="s">
-        <v>5673</v>
+        <v>5675</v>
       </c>
       <c r="C2100" t="s">
         <v>9</v>
       </c>
       <c r="D2100" t="s">
-        <v>22</v>
+        <v>175</v>
       </c>
       <c r="E2100" t="s">
-        <v>23</v>
+        <v>176</v>
       </c>
       <c r="F2100" t="s">
-        <v>5674</v>
+        <v>5676</v>
       </c>
       <c r="G2100" t="s">
         <v>2498</v>
@@ -63344,7 +63452,7 @@
     </row>
     <row r="2101" spans="1:7">
       <c r="A2101" t="s">
-        <v>5675</v>
+        <v>5677</v>
       </c>
       <c r="C2101" t="s">
         <v>9</v>
@@ -63356,35 +63464,35 @@
         <v>176</v>
       </c>
       <c r="F2101" t="s">
-        <v>5676</v>
+        <v>5678</v>
       </c>
       <c r="G2101" t="s">
-        <v>2795</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2102" spans="1:7">
       <c r="A2102" t="s">
-        <v>5677</v>
+        <v>5679</v>
       </c>
       <c r="C2102" t="s">
         <v>9</v>
       </c>
       <c r="D2102" t="s">
-        <v>10</v>
+        <v>175</v>
       </c>
       <c r="E2102" t="s">
-        <v>11</v>
+        <v>176</v>
       </c>
       <c r="F2102" t="s">
-        <v>5678</v>
+        <v>5680</v>
       </c>
       <c r="G2102" t="s">
-        <v>5299</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2103" spans="1:7">
       <c r="A2103" t="s">
-        <v>5679</v>
+        <v>5681</v>
       </c>
       <c r="C2103" t="s">
         <v>9</v>
@@ -63396,7 +63504,7 @@
         <v>32</v>
       </c>
       <c r="F2103" t="s">
-        <v>5680</v>
+        <v>5682</v>
       </c>
       <c r="G2103" t="s">
         <v>47</v>
@@ -63404,87 +63512,81 @@
     </row>
     <row r="2104" spans="1:7">
       <c r="A2104" t="s">
-        <v>5681</v>
+        <v>5683</v>
       </c>
       <c r="C2104" t="s">
         <v>9</v>
       </c>
       <c r="D2104" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2104" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2104" t="s">
-        <v>5682</v>
+        <v>5684</v>
       </c>
       <c r="G2104" t="s">
-        <v>47</v>
+        <v>926</v>
       </c>
     </row>
     <row r="2105" spans="1:7">
       <c r="A2105" t="s">
-        <v>5683</v>
+        <v>5685</v>
       </c>
       <c r="C2105" t="s">
         <v>9</v>
       </c>
-      <c r="D2105" t="s">
-        <v>31</v>
-      </c>
-      <c r="E2105" t="s">
-        <v>32</v>
-      </c>
       <c r="F2105" t="s">
-        <v>5684</v>
+        <v>5686</v>
       </c>
       <c r="G2105" t="s">
-        <v>47</v>
+        <v>437</v>
       </c>
     </row>
     <row r="2106" spans="1:7">
       <c r="A2106" t="s">
-        <v>5685</v>
+        <v>5687</v>
       </c>
       <c r="C2106" t="s">
         <v>9</v>
       </c>
       <c r="D2106" t="s">
-        <v>22</v>
+        <v>370</v>
       </c>
       <c r="E2106" t="s">
-        <v>23</v>
+        <v>371</v>
       </c>
       <c r="F2106" t="s">
-        <v>5686</v>
+        <v>5688</v>
       </c>
       <c r="G2106" t="s">
-        <v>47</v>
+        <v>3610</v>
       </c>
     </row>
     <row r="2107" spans="1:7">
       <c r="A2107" t="s">
-        <v>5687</v>
+        <v>5689</v>
       </c>
       <c r="C2107" t="s">
         <v>9</v>
       </c>
       <c r="D2107" t="s">
-        <v>290</v>
+        <v>31</v>
       </c>
       <c r="E2107" t="s">
-        <v>291</v>
+        <v>32</v>
       </c>
       <c r="F2107" t="s">
-        <v>5688</v>
+        <v>5690</v>
       </c>
       <c r="G2107" t="s">
-        <v>437</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2108" spans="1:7">
       <c r="A2108" t="s">
-        <v>5689</v>
+        <v>5691</v>
       </c>
       <c r="C2108" t="s">
         <v>9</v>
@@ -63496,72 +63598,366 @@
         <v>176</v>
       </c>
       <c r="F2108" t="s">
-        <v>5690</v>
+        <v>5692</v>
       </c>
       <c r="G2108" t="s">
-        <v>358</v>
+        <v>1911</v>
       </c>
     </row>
     <row r="2109" spans="1:7">
       <c r="A2109" t="s">
-        <v>5691</v>
+        <v>5693</v>
       </c>
       <c r="C2109" t="s">
         <v>9</v>
       </c>
       <c r="D2109" t="s">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="E2109" t="s">
-        <v>32</v>
+        <v>176</v>
       </c>
       <c r="F2109" t="s">
-        <v>5692</v>
+        <v>5694</v>
       </c>
       <c r="G2109" t="s">
-        <v>47</v>
+        <v>5642</v>
       </c>
     </row>
     <row r="2110" spans="1:7">
       <c r="A2110" t="s">
-        <v>5693</v>
+        <v>5695</v>
       </c>
       <c r="C2110" t="s">
-        <v>42</v>
+        <v>9</v>
       </c>
       <c r="D2110" t="s">
-        <v>290</v>
+        <v>175</v>
       </c>
       <c r="E2110" t="s">
-        <v>291</v>
+        <v>176</v>
       </c>
       <c r="F2110" t="s">
-        <v>4754</v>
+        <v>5696</v>
       </c>
       <c r="G2110" t="s">
-        <v>1689</v>
+        <v>5549</v>
       </c>
     </row>
     <row r="2111" spans="1:7">
       <c r="A2111" t="s">
-        <v>5694</v>
-      </c>
-      <c r="B2111" t="s">
-        <v>5695</v>
+        <v>5697</v>
       </c>
       <c r="C2111" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2111" t="s">
+        <v>5698</v>
+      </c>
+      <c r="G2111" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:7">
+      <c r="A2112" t="s">
+        <v>5699</v>
+      </c>
+      <c r="C2112" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2112" t="s">
+        <v>120</v>
+      </c>
+      <c r="E2112" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2112" t="s">
+        <v>5700</v>
+      </c>
+      <c r="G2112" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:7">
+      <c r="A2113" t="s">
+        <v>5701</v>
+      </c>
+      <c r="C2113" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2113" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2113" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2113" t="s">
+        <v>5702</v>
+      </c>
+      <c r="G2113" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:7">
+      <c r="A2114" t="s">
+        <v>5703</v>
+      </c>
+      <c r="C2114" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2114" t="s">
+        <v>370</v>
+      </c>
+      <c r="E2114" t="s">
+        <v>371</v>
+      </c>
+      <c r="F2114" t="s">
+        <v>5704</v>
+      </c>
+      <c r="G2114" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:7">
+      <c r="A2115" t="s">
+        <v>5705</v>
+      </c>
+      <c r="C2115" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2115" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2115" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2115" t="s">
+        <v>5706</v>
+      </c>
+      <c r="G2115" t="s">
+        <v>2498</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:7">
+      <c r="A2116" t="s">
+        <v>5707</v>
+      </c>
+      <c r="C2116" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2116" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2116" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2116" t="s">
+        <v>5708</v>
+      </c>
+      <c r="G2116" t="s">
+        <v>2795</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:7">
+      <c r="A2117" t="s">
+        <v>5709</v>
+      </c>
+      <c r="C2117" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2117" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2117" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2117" t="s">
+        <v>5710</v>
+      </c>
+      <c r="G2117" t="s">
+        <v>5299</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:7">
+      <c r="A2118" t="s">
+        <v>5711</v>
+      </c>
+      <c r="C2118" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2118" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2118" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2118" t="s">
+        <v>5712</v>
+      </c>
+      <c r="G2118" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:7">
+      <c r="A2119" t="s">
+        <v>5713</v>
+      </c>
+      <c r="C2119" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2119" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2119" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2119" t="s">
+        <v>5714</v>
+      </c>
+      <c r="G2119" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:7">
+      <c r="A2120" t="s">
+        <v>5715</v>
+      </c>
+      <c r="C2120" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2120" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2120" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2120" t="s">
+        <v>5716</v>
+      </c>
+      <c r="G2120" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:7">
+      <c r="A2121" t="s">
+        <v>5717</v>
+      </c>
+      <c r="C2121" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2121" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2121" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2121" t="s">
+        <v>5718</v>
+      </c>
+      <c r="G2121" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:7">
+      <c r="A2122" t="s">
+        <v>5719</v>
+      </c>
+      <c r="C2122" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2122" t="s">
+        <v>290</v>
+      </c>
+      <c r="E2122" t="s">
+        <v>291</v>
+      </c>
+      <c r="F2122" t="s">
+        <v>5720</v>
+      </c>
+      <c r="G2122" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:7">
+      <c r="A2123" t="s">
+        <v>5721</v>
+      </c>
+      <c r="C2123" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2123" t="s">
+        <v>175</v>
+      </c>
+      <c r="E2123" t="s">
+        <v>176</v>
+      </c>
+      <c r="F2123" t="s">
+        <v>5722</v>
+      </c>
+      <c r="G2123" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:7">
+      <c r="A2124" t="s">
+        <v>5723</v>
+      </c>
+      <c r="C2124" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2124" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2124" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2124" t="s">
+        <v>5724</v>
+      </c>
+      <c r="G2124" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:7">
+      <c r="A2125" t="s">
+        <v>5725</v>
+      </c>
+      <c r="C2125" t="s">
         <v>42</v>
       </c>
-      <c r="D2111" t="s">
+      <c r="D2125" t="s">
+        <v>290</v>
+      </c>
+      <c r="E2125" t="s">
+        <v>291</v>
+      </c>
+      <c r="F2125" t="s">
+        <v>4754</v>
+      </c>
+      <c r="G2125" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:7">
+      <c r="A2126" t="s">
+        <v>5726</v>
+      </c>
+      <c r="B2126" t="s">
+        <v>5727</v>
+      </c>
+      <c r="C2126" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2126" t="s">
         <v>370</v>
       </c>
-      <c r="E2111" t="s">
+      <c r="E2126" t="s">
         <v>371</v>
       </c>
-      <c r="F2111" t="s">
-        <v>5696</v>
-      </c>
-      <c r="G2111" t="s">
+      <c r="F2126" t="s">
+        <v>5728</v>
+      </c>
+      <c r="G2126" t="s">
         <v>525</v>
       </c>
     </row>
